--- a/data/merged/2026-09-28/MERGED_FR_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_FR_Mite-Vacuum_2026-09-28.xlsx
@@ -4933,13 +4933,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4977,13 +4977,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5021,13 +5021,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5065,13 +5065,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5109,13 +5109,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5153,13 +5153,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5197,13 +5197,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5241,13 +5241,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5285,13 +5285,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5329,13 +5329,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5694,7 +5694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR40"/>
+  <dimension ref="A1:BR39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -11386,52 +11386,53 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Marque: Hocomay | Caractéristique spéciale: Rechargeable | Recommandation de surface: Bed | Sans fil ?: Oui | Poids de l'article: 2300 Grammes | Facteur de forme: Portatif | Couleur: Blanc. | Dimensions du produit: 29L x 27l x 18H centimètres | Fabricant: Hocomay | Nombre d'articles: 1</t>
+          <t>Marque: Tiazhan | Caractéristique spéciale: HEPA, Rayons ultraviolets, chauffage | Type de filtre: Filtre HEPA | Recommandation de surface: Tapis, Tapisserie | Source d'alimentation: Câble électrique | Composants inclus: Filtre HEPA 2 réservoirs de poussière 500 ml | Sans fil ?: Non | Capacité: 500 ml | Utilisations recommandées pour le produit: tissus d'ameublement, tapis, matelas, zones difficiles d'accès, nettoyage des taches | Facteur de forme: Portatif</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Hocomay</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Hocomay</t>
+          <t>https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur sans fil avec lumière UV-C, aspirateur à main 16 kPa avec écran LED, filtre HEPA, ultrasons, aspirateur de lit double tasse pour lit, canapé et coussin</t>
+          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 W| Élimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiéreurs Doubles de0.5L,pour Convient aux Lits et aux Canapés</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de matelas sans fil : cet aspirateur anti-acariens a une batterie intégrée de 1800 mAh qui se recharge via un câble USB de type C et un câble USB, la seule autonomie de la batterie est jusqu'à 30 minutes, et il n'est pas nécessaire de connecter une source d'alimentation lorsque vous l'utilisez. La conception sans fil vous permet de l'utiliser librement, pas besoin de vous soucier de la longueur du câble.
-Double bac à poussière amovible : l'aspirateur à matelas est un design de grande capacité avec deux ventouses, avec une capacité de collecte de poussière maximale de 520 ml, ce qui résout le problème de devoir vider la poussière fréquemment. L'anti-acariens adopte des filtres HEPA qui peuvent bien séparer les particules fines, prévenir efficacement l'obstruction et prolonger la durée de vie du filtre.
-Lampe UV-C et ultrasons : l'aspirateur pour matelas à main a une lumière UV-C, la source de lumière couvre la surface du lit en contact pour obtenir l'élimination des bactéries et des acariens. L'anti-acariens émet des ondes ultrasoniques à haute fréquence inoffensives lors du fonctionnement pour détruire la structure des acariens et des bactéries et créer un environnement propre.
-Forte puissance d'aspiration de 16 Kpa : l'aspirateur de lit a une puissance d'aspiration allant jusqu'à 16 000 PA, qui atteint profondément le matelas pour terminer le nettoyage efficacement et rapidement. En même temps, la brosse à rouleau vibre à une fréquence élevée de 18 000 coups par minute pour nettoyer efficacement la saleté et les bactéries cachées.
-Écran LED haute résolution : l'aspirateur de matelas sans fil portatif a deux vitesses qui peuvent être réglées, et les vitesses et les modes sont clairement visibles grâce à l'écran LED. L'aspirateur est facile à utiliser avec un interrupteur à une touche, il suffit d'appuyer longuement sur le bouton pour l'allumer.</t>
+          <t>【Nettoyage en Profondeur très Efficace】Ce aspirateur matelas anti acariens dispose d'une puissance d'aspiration , associée à un moteur de 400 W et une brosse rotative atteignant 40 000 tr/min. Cette combinaison permet à aspirateur anti acariens d'éliminer profondément la poussière, les squames et les particules incrustées. Il garantit un environnement plus sain pour toute la famille, faisant de ce appareil un anti acarien performant pour un sommeil paisible.
+【Technologie UV-C Avancée】Équipé d'une lampe UV à 253,7 nm, cet aspirateur matelas anti acariens pénètre en profondeur dans les fibres pour éradiquer 99,9 % des micro-organismes et allergènes. La aspirateur anti acariens canapé et matelas nettoie en profondeur les surfaces textiles, assurant un cadre de vie plus sain et agréable pour tous les membres de la famille.
+【Système de Filtration HEPA】Cet aspirateur matelas anti acariens est muni d'un système de filtration multicouche, avec un filtre HEPA haute performance capturant 99,97 % des particules jusqu'à 0,3 micron. Le filtre est démontable et lavable facilement, ce qui renforce l'efficacité du aspirateur anti acariens et prolonge sa durée de vie pour un entretien régulier et hygiénique.
+【Double bac de Récupération de Poussière】Avec deux bacs à poussière de 500 ml, cet aspirateur matelas anti acariens optimise la séparation poussière-saleté, augmentant ainsi sa capacité de rétention. Le système double bac évite la contamination croisée et rend le nettoyage plus efficace et hygiénique, un atout majeur pour cet aspirateur matelas quotidien.
+【Fonction Air Chaud】Cet aspirateur matelas anti acariens projette de l'air chaud à 60 °C, simulant l'effet du soleil. couplée à la brosse, cette fonction permet de pénétrer le matelas, stériliser à haute température et maintenir la sécheresse. Idéal pour les climats humides, ce aspirateur matelas élimine les acariens et garde les textiles secs et sains.
+【Sûr et Fiable】Le démarrage par simple pression (maintenue deux secondes) et le double mode de nettoyage rendent cet aspirateur matelas anti acariens facile et sécurisé à utiliser. Conçu avec des matériaux durables, cet aspirateur anti acariens assure un fonctionnement stable et réduit la fréquence de maintenance, une solution fiable surtout pour les foyers avec enfants ou animaux.</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -11445,7 +11446,7 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>2515997</v>
+        <v>1171906</v>
       </c>
       <c r="P25" s="15"/>
       <c r="Q25" s="16">
@@ -11458,7 +11459,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -11470,37 +11471,37 @@
         <v>1</v>
       </c>
       <c r="Z25" s="20">
-        <v>49.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA25" s="4"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE25" s="15">
         <v>0</v>
       </c>
       <c r="AF25" s="21">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
       </c>
       <c r="AH25" s="20">
-        <v>9.77</v>
+        <v>8.34</v>
       </c>
       <c r="AI25" s="16">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AL25" s="19">
-        <v>494</v>
+        <v>336</v>
       </c>
       <c r="AM25" s="13" t="inlineStr">
         <is>
@@ -11511,14 +11512,14 @@
       <c r="AO25" s="13"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR25" s="19">
         <v>1</v>
       </c>
       <c r="AS25" s="14" t="inlineStr">
         <is>
-          <t>Luckily Baby</t>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
         </is>
       </c>
       <c r="AT25" s="13" t="inlineStr">
@@ -11528,17 +11529,17 @@
       </c>
       <c r="AU25" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV25" s="14" t="inlineStr">
         <is>
-          <t>武汉市 湖北省 430040 CN</t>
+          <t>NORTHERN IRELAND BT2 7FD GB</t>
         </is>
       </c>
       <c r="AW25" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JWI8CSWZ8XWG</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
         </is>
       </c>
       <c r="AX25" s="13"/>
@@ -11546,7 +11547,11 @@
       <c r="AZ25" s="13"/>
       <c r="BA25" s="13"/>
       <c r="BB25" s="13"/>
-      <c r="BC25" s="13"/>
+      <c r="BC25" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD25" s="13"/>
       <c r="BE25" s="13"/>
       <c r="BF25" s="13"/>
@@ -11555,25 +11560,45 @@
       <c r="BI25" s="23"/>
       <c r="BJ25" s="23" t="inlineStr">
         <is>
-          <t>2300 Grammes</t>
+          <t>2,06 Kilograms</t>
         </is>
       </c>
       <c r="BK25" s="23" t="inlineStr">
         <is>
-          <t>2.30 kg</t>
+          <t>2.06 kg</t>
         </is>
       </c>
       <c r="BL25" s="23" t="inlineStr">
         <is>
-          <t>29L x 27l x 18H centimètres</t>
+          <t>28L x 15l x 68H centimètres</t>
         </is>
       </c>
       <c r="BM25" s="23"/>
-      <c r="BN25" s="23"/>
-      <c r="BO25" s="23"/>
-      <c r="BP25" s="23"/>
-      <c r="BQ25" s="23"/>
-      <c r="BR25" s="13"/>
+      <c r="BN25" s="23" t="inlineStr">
+        <is>
+          <t>2.06 kg</t>
+        </is>
+      </c>
+      <c r="BO25" s="23" t="inlineStr">
+        <is>
+          <t>2.06 kg</t>
+        </is>
+      </c>
+      <c r="BP25" s="23" t="inlineStr">
+        <is>
+          <t>34.4 x 28.5 x 22.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ25" s="23" t="inlineStr">
+        <is>
+          <t>34.40 x 28.50 x 22.20 cm</t>
+        </is>
+      </c>
+      <c r="BR25" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -11582,53 +11607,52 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Marque: Tiazhan | Caractéristique spéciale: HEPA, Rayons ultraviolets, chauffage | Type de filtre: Filtre HEPA | Recommandation de surface: Tapis, Tapisserie | Source d'alimentation: Câble électrique | Composants inclus: Filtre HEPA 2 réservoirs de poussière 500 ml | Sans fil ?: Non | Capacité: 500 ml | Utilisations recommandées pour le produit: tissus d'ameublement, tapis, matelas, zones difficiles d'accès, nettoyage des taches | Facteur de forme: Portatif</t>
+          <t>Marque: Liwankaqi | Caractéristique spéciale: Stemless | Type de filtre: Tissu | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Tension: 523 Volts | Composants inclus: Mite Remover | Sans fil ?: Oui | Poids de l'article: 2235 Grammes | Capacité: 520 ml</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 W| Élimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiéreurs Doubles de0.5L,pour Convient aux Lits et aux Canapés</t>
+          <t>Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit, canapé, tapis et plus encore</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>【Nettoyage en Profondeur très Efficace】Ce aspirateur matelas anti acariens dispose d'une puissance d'aspiration , associée à un moteur de 400 W et une brosse rotative atteignant 40 000 tr/min. Cette combinaison permet à aspirateur anti acariens d'éliminer profondément la poussière, les squames et les particules incrustées. Il garantit un environnement plus sain pour toute la famille, faisant de ce appareil un anti acarien performant pour un sommeil paisible.
-【Technologie UV-C Avancée】Équipé d'une lampe UV à 253,7 nm, cet aspirateur matelas anti acariens pénètre en profondeur dans les fibres pour éradiquer 99,9 % des micro-organismes et allergènes. La aspirateur anti acariens canapé et matelas nettoie en profondeur les surfaces textiles, assurant un cadre de vie plus sain et agréable pour tous les membres de la famille.
-【Système de Filtration HEPA】Cet aspirateur matelas anti acariens est muni d'un système de filtration multicouche, avec un filtre HEPA haute performance capturant 99,97 % des particules jusqu'à 0,3 micron. Le filtre est démontable et lavable facilement, ce qui renforce l'efficacité du aspirateur anti acariens et prolonge sa durée de vie pour un entretien régulier et hygiénique.
-【Double bac de Récupération de Poussière】Avec deux bacs à poussière de 500 ml, cet aspirateur matelas anti acariens optimise la séparation poussière-saleté, augmentant ainsi sa capacité de rétention. Le système double bac évite la contamination croisée et rend le nettoyage plus efficace et hygiénique, un atout majeur pour cet aspirateur matelas quotidien.
-【Fonction Air Chaud】Cet aspirateur matelas anti acariens projette de l'air chaud à 60 °C, simulant l'effet du soleil. couplée à la brosse, cette fonction permet de pénétrer le matelas, stériliser à haute température et maintenir la sécheresse. Idéal pour les climats humides, ce aspirateur matelas élimine les acariens et garde les textiles secs et sains.
-【Sûr et Fiable】Le démarrage par simple pression (maintenue deux secondes) et le double mode de nettoyage rendent cet aspirateur matelas anti acariens facile et sécurisé à utiliser. Conçu avec des matériaux durables, cet aspirateur anti acariens assure un fonctionnement stable et réduit la fréquence de maintenance, une solution fiable surtout pour les foyers avec enfants ou animaux.</t>
+          <t>[Deux modes d'aspiration puissants pour une hygiène parfaite] : notre aspirateur anti-acariens pour matelas offre deux niveaux de puissance, idéal pour les personnes allergiques ! La forte aspiration élimine efficacement les acariens, la poussière et les squames. Parfait comme aspirateur humide pour un environnement de sommeil hygiénique et propre
+[Technologie UV &amp; Haute Fréquence Anti-Acariens] : l'aspirateur anti-acariens UV combine 4 principes d'action: désinfection UV C, ultrasons, rotation de la brosse et aspiration 8000Pa. Ainsi, 99,9 % des acariens et des bactéries sont éliminés scientifiquement
+Système innovant à 2 chambres avec volume de 520 ml : l'aspirateur anti-acariens pour matelas sépare efficacement les allergènes et la poussière grâce au filtre HEPA et au récipient transparent. Grand volume pour moins de vides, pratique pour les familles
+[Léger et intuitif] : manipulation facile grâce au design ergonomique de l'aspirateur à main. Les composants peuvent être rapidement démontés et nettoyés. Particulièrement adapté aux personnes âgées et aux foyers allergiques
+Utilisation universelle dans toute la maison : pas seulement pour les matelas. Idéal pour les canapés, les tapis, les sièges de voiture et les paniers pour animaux. Ce puissant appareil polyvalent remplace les appareils spéciaux coûteux - Votre partenaire hygiénique pratique pour chaque pièce</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -11642,7 +11666,7 @@
         </is>
       </c>
       <c r="O26" s="15">
-        <v>1171906</v>
+        <v>2400585</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="16">
@@ -11655,7 +11679,7 @@
       </c>
       <c r="S26" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T26" s="15"/>
@@ -11666,39 +11690,27 @@
       <c r="Y26" s="19">
         <v>1</v>
       </c>
-      <c r="Z26" s="20">
-        <v>65.99</v>
-      </c>
+      <c r="Z26" s="20"/>
       <c r="AA26" s="4"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>10</v>
-      </c>
-      <c r="AE26" s="15">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
-      <c r="AH26" s="20">
-        <v>8.34</v>
-      </c>
+      <c r="AH26" s="20"/>
       <c r="AI26" s="16">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AJ26"/>
-      <c r="AK26" s="13" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AL26" s="19">
-        <v>336</v>
-      </c>
+      <c r="AK26" s="13"/>
+      <c r="AL26" s="19"/>
       <c r="AM26" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -11707,37 +11719,17 @@
       <c r="AN26" s="13"/>
       <c r="AO26" s="13"/>
       <c r="AP26" s="4"/>
-      <c r="AQ26" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR26" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS26" s="14" t="inlineStr">
-        <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
-        </is>
-      </c>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="14"/>
       <c r="AT26" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU26" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV26" s="14" t="inlineStr">
-        <is>
-          <t>NORTHERN IRELAND BT2 7FD GB</t>
-        </is>
-      </c>
-      <c r="AW26" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
-        </is>
-      </c>
+      <c r="AU26" s="13"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="13"/>
       <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
       <c r="AZ26" s="13"/>
@@ -11748,7 +11740,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD26" s="13"/>
+      <c r="BD26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
@@ -11756,45 +11752,25 @@
       <c r="BI26" s="23"/>
       <c r="BJ26" s="23" t="inlineStr">
         <is>
-          <t>2,06 Kilograms</t>
+          <t>2235 Grammes</t>
         </is>
       </c>
       <c r="BK26" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BL26" s="23" t="inlineStr">
         <is>
-          <t>28L x 15l x 68H centimètres</t>
+          <t>29,5L x 2,7l x 18,5H centimètres</t>
         </is>
       </c>
       <c r="BM26" s="23"/>
-      <c r="BN26" s="23" t="inlineStr">
-        <is>
-          <t>2.06 kg</t>
-        </is>
-      </c>
-      <c r="BO26" s="23" t="inlineStr">
-        <is>
-          <t>2.06 kg</t>
-        </is>
-      </c>
-      <c r="BP26" s="23" t="inlineStr">
-        <is>
-          <t>34.4 x 28.5 x 22.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ26" s="23" t="inlineStr">
-        <is>
-          <t>34.40 x 28.50 x 22.20 cm</t>
-        </is>
-      </c>
-      <c r="BR26" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN26" s="23"/>
+      <c r="BO26" s="23"/>
+      <c r="BP26" s="23"/>
+      <c r="BQ26" s="23"/>
+      <c r="BR26" s="13"/>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
@@ -11803,52 +11779,48 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Marque: Liwankaqi | Caractéristique spéciale: Stemless | Type de filtre: Tissu | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Tension: 523 Volts | Composants inclus: Mite Remover | Sans fil ?: Oui | Poids de l'article: 2235 Grammes | Capacité: 520 ml</t>
+          <t>Marque: JIGOO | Caractéristique spéciale: Hypoallergénique | Type de filtre: Filtre HEPA | Recommandation de surface: Tapisserie, tapis | Source d'alimentation: Alimenté par batterie | Composants inclus: Brosse à épousseter, Suceur plat | Sans fil ?: Oui | Utilisations recommandées pour le produit: matelas et rembourrage | Facteur de forme: Portatif | Couleur: Vert</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit, canapé, tapis et plus encore</t>
+          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>[Deux modes d'aspiration puissants pour une hygiène parfaite] : notre aspirateur anti-acariens pour matelas offre deux niveaux de puissance, idéal pour les personnes allergiques ! La forte aspiration élimine efficacement les acariens, la poussière et les squames. Parfait comme aspirateur humide pour un environnement de sommeil hygiénique et propre
-[Technologie UV &amp; Haute Fréquence Anti-Acariens] : l'aspirateur anti-acariens UV combine 4 principes d'action: désinfection UV C, ultrasons, rotation de la brosse et aspiration 8000Pa. Ainsi, 99,9 % des acariens et des bactéries sont éliminés scientifiquement
-Système innovant à 2 chambres avec volume de 520 ml : l'aspirateur anti-acariens pour matelas sépare efficacement les allergènes et la poussière grâce au filtre HEPA et au récipient transparent. Grand volume pour moins de vides, pratique pour les familles
-[Léger et intuitif] : manipulation facile grâce au design ergonomique de l'aspirateur à main. Les composants peuvent être rapidement démontés et nettoyés. Particulièrement adapté aux personnes âgées et aux foyers allergiques
-Utilisation universelle dans toute la maison : pas seulement pour les matelas. Idéal pour les canapés, les tapis, les sièges de voiture et les paniers pour animaux. Ce puissant appareil polyvalent remplace les appareils spéciaux coûteux - Votre partenaire hygiénique pratique pour chaque pièce</t>
+          <t>JIGOO T600 Aspirateur anti-acariens pour matelas : Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -11862,7 +11834,7 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>2400585</v>
+        <v>1528398</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="16">
@@ -11875,7 +11847,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -11891,11 +11863,11 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE27" s="15"/>
       <c r="AF27" s="21">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -11931,34 +11903,22 @@
       <c r="AZ27" s="13"/>
       <c r="BA27" s="13"/>
       <c r="BB27" s="13"/>
-      <c r="BC27" s="13" t="inlineStr">
+      <c r="BC27" s="13"/>
+      <c r="BD27" s="13"/>
+      <c r="BE27" s="13"/>
+      <c r="BF27" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD27" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE27" s="13"/>
-      <c r="BF27" s="13"/>
       <c r="BG27" s="13"/>
       <c r="BH27" s="14"/>
       <c r="BI27" s="23"/>
-      <c r="BJ27" s="23" t="inlineStr">
-        <is>
-          <t>2235 Grammes</t>
-        </is>
-      </c>
-      <c r="BK27" s="23" t="inlineStr">
-        <is>
-          <t>2.24 kg</t>
-        </is>
-      </c>
+      <c r="BJ27" s="23"/>
+      <c r="BK27" s="23"/>
       <c r="BL27" s="23" t="inlineStr">
         <is>
-          <t>29,5L x 2,7l x 18,5H centimètres</t>
+          <t>6L x 1,3l x 8H centimètres</t>
         </is>
       </c>
       <c r="BM27" s="23"/>
@@ -11975,48 +11935,48 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Marque: JIGOO | Caractéristique spéciale: Hypoallergénique | Type de filtre: Filtre HEPA | Recommandation de surface: Tapisserie, tapis | Source d'alimentation: Alimenté par batterie | Composants inclus: Brosse à épousseter, Suceur plat | Sans fil ?: Oui | Utilisations recommandées pour le produit: matelas et rembourrage | Facteur de forme: Portatif | Couleur: Vert</t>
+          <t>Marque: Minthouz | Caractéristique spéciale: Lumière UV | Type de filtre: Filtre HEPA | Recommandation de surface: Rembourrage | Source d'alimentation: Câble électrique | Sans fil ?: Non | Utilisations recommandées pour le produit: rembourrage, assainissement | Facteur de forme: Portatif | Couleur: Noir | Nom de modèle: MT-M302</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur Anti-acariens</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens pour matelas : Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur anti-acariens</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -12030,7 +11990,7 @@
         </is>
       </c>
       <c r="O28" s="15">
-        <v>1528398</v>
+        <v>1333721</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="16">
@@ -12043,7 +12003,7 @@
       </c>
       <c r="S28" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T28" s="15"/>
@@ -12054,27 +12014,39 @@
       <c r="Y28" s="19">
         <v>1</v>
       </c>
-      <c r="Z28" s="20"/>
+      <c r="Z28" s="20">
+        <v>96.44</v>
+      </c>
       <c r="AA28" s="4"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>10</v>
-      </c>
-      <c r="AE28" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="AE28" s="15">
+        <v>1</v>
+      </c>
       <c r="AF28" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
       </c>
-      <c r="AH28" s="20"/>
+      <c r="AH28" s="20">
+        <v>8.11</v>
+      </c>
       <c r="AI28" s="16">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AJ28"/>
-      <c r="AK28" s="13"/>
-      <c r="AL28" s="19"/>
+      <c r="AK28" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AL28" s="19">
+        <v>155</v>
+      </c>
       <c r="AM28" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12083,17 +12055,37 @@
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
       <c r="AP28" s="4"/>
-      <c r="AQ28" s="19"/>
-      <c r="AR28" s="19"/>
-      <c r="AS28" s="14"/>
+      <c r="AQ28" s="19">
+        <v>5</v>
+      </c>
+      <c r="AR28" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS28" s="14" t="inlineStr">
+        <is>
+          <t>Minthouz EUDirect</t>
+        </is>
+      </c>
       <c r="AT28" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU28" s="13"/>
-      <c r="AV28" s="14"/>
-      <c r="AW28" s="13"/>
+      <c r="AU28" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV28" s="14" t="inlineStr">
+        <is>
+          <t>guangmingqu Guangdong 518100 CN</t>
+        </is>
+      </c>
+      <c r="AW28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
+        </is>
+      </c>
       <c r="AX28" s="13"/>
       <c r="AY28" s="13"/>
       <c r="AZ28" s="13"/>
@@ -12102,27 +12094,51 @@
       <c r="BC28" s="13"/>
       <c r="BD28" s="13"/>
       <c r="BE28" s="13"/>
-      <c r="BF28" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF28" s="13"/>
       <c r="BG28" s="13"/>
       <c r="BH28" s="14"/>
       <c r="BI28" s="23"/>
-      <c r="BJ28" s="23"/>
-      <c r="BK28" s="23"/>
+      <c r="BJ28" s="23" t="inlineStr">
+        <is>
+          <t>3,6 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK28" s="23" t="inlineStr">
+        <is>
+          <t>3.60 kg</t>
+        </is>
+      </c>
       <c r="BL28" s="23" t="inlineStr">
         <is>
-          <t>6L x 1,3l x 8H centimètres</t>
+          <t>31,2L x 31,2l x 23,8H centimètres</t>
         </is>
       </c>
       <c r="BM28" s="23"/>
-      <c r="BN28" s="23"/>
-      <c r="BO28" s="23"/>
-      <c r="BP28" s="23"/>
-      <c r="BQ28" s="23"/>
-      <c r="BR28" s="13"/>
+      <c r="BN28" s="23" t="inlineStr">
+        <is>
+          <t>3.6 kg</t>
+        </is>
+      </c>
+      <c r="BO28" s="23" t="inlineStr">
+        <is>
+          <t>3.60 kg</t>
+        </is>
+      </c>
+      <c r="BP28" s="23" t="inlineStr">
+        <is>
+          <t>31 x 31 x 23.7 cm</t>
+        </is>
+      </c>
+      <c r="BQ28" s="23" t="inlineStr">
+        <is>
+          <t>31.00 x 31.00 x 23.70 cm</t>
+        </is>
+      </c>
+      <c r="BR28" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
@@ -12131,48 +12147,52 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Marque: Minthouz | Caractéristique spéciale: Lumière UV | Type de filtre: Filtre HEPA | Recommandation de surface: Rembourrage | Source d'alimentation: Câble électrique | Sans fil ?: Non | Utilisations recommandées pour le produit: rembourrage, assainissement | Facteur de forme: Portatif | Couleur: Noir | Nom de modèle: MT-M302</t>
+          <t>Marque: Yaasier | Caractéristique spéciale: Lumière UV | Type de filtre: Filtre HEPA | Recommandation de surface: Tapis, Rembourrage | Source d'alimentation: Alimenté par batterie | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, coussins, canapés, tapis | Facteur de forme: Portatif | Couleur: Blanc. | Nom de modèle: 1X1BSCMY</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Minthouz</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur Anti-acariens</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99% de Tous Les acariens pour Lits, oreillers, canapés et Tapis</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur anti-acariens</t>
+          <t>Technologie avancée 3 en 1 : équipé d'un aspirateur anti-acariens [technologie avancée trois en un] Équipé d'un tampon de pulsation double battement et d'une lumière UV de 253,7 nm, cet aspirateur offre une grande zone de nettoyage et une efficacité accrue, idéal pour éliminer les acariens et autres allergènes de vos matelas et textiles. Avec un tampon de pulsation double Beat et 253,7 La lumière UV nm fournit cette l'aspirateur offre une grande zone de nettoyage et une efficacité accrue, idéal pour éliminer les acariens et autres allergènes de vos matelas et textiles.
+[Design sans fil léger] Maximisez votre confort avec cet aspirateur sans fil léger qui dispose d'une batterie rechargeable qui offre une autonomie allant jusqu'à 30 minutes. Son design moderne et élégant s'intègre parfaitement dans n'importe quel intérieur et rend le nettoyage sans effort.
+[Système de filtration à haute efficacité] Nettoyeur de matelas avec un filtre HEPA lavable et un filtre en coton sur la sortie, cet aspirateur capture 99,97 % des particules de poussière fine, assure un air plus sain et réduit la pollution secondaire - Idéal pour les personnes sensibles et les familles avec enfants.
+[Bac à poussière lavable et facile à nettoyer] Aspirateur anti-acariens avec le bac à poussière lavable à l'eau courante, votre aspirateur est plus facile à nettoyer. Séchez le filtre avant la réutilisation pour assurer une puissance d'aspiration optimale et des performances de nettoyage constantes.
+Polyvalence et confort d'utilisation : aspirateur anti-acariens avec lumière UV, idéal pour aspirer les poils d'animaux et les squames sur différentes surfaces en tissu telles que les matelas, les coussins, les canapés et les tapis. Profitez d'un nettoyage silencieux qui ne dérange pas les bébés ou les animaux domestiques endormis.</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -12186,11 +12206,13 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>1333721</v>
-      </c>
-      <c r="P29" s="15"/>
+        <v>2257594</v>
+      </c>
+      <c r="P29" s="15">
+        <v>-17555</v>
+      </c>
       <c r="Q29" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
@@ -12199,7 +12221,7 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T29" s="15"/>
@@ -12211,37 +12233,37 @@
         <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>96.44</v>
+        <v>28.99</v>
       </c>
       <c r="AA29" s="4"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="AE29" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
       </c>
       <c r="AH29" s="20">
-        <v>8.11</v>
+        <v>5.98</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>155</v>
+        <v>296</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -12252,14 +12274,14 @@
       <c r="AO29" s="13"/>
       <c r="AP29" s="4"/>
       <c r="AQ29" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR29" s="19">
         <v>1</v>
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Minthouz EUDirect</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
@@ -12274,12 +12296,12 @@
       </c>
       <c r="AV29" s="14" t="inlineStr">
         <is>
-          <t>guangmingqu Guangdong 518100 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW29" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX29" s="13"/>
@@ -12287,7 +12309,11 @@
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13"/>
+      <c r="BC29" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD29" s="13"/>
       <c r="BE29" s="13"/>
       <c r="BF29" s="13"/>
@@ -12296,43 +12322,43 @@
       <c r="BI29" s="23"/>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>3,6 Kilograms</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>31,2L x 31,2l x 23,8H centimètres</t>
+          <t>6L x 4l x 8H centimètres</t>
         </is>
       </c>
       <c r="BM29" s="23"/>
       <c r="BN29" s="23" t="inlineStr">
         <is>
-          <t>3.6 kg</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BO29" s="23" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BP29" s="23" t="inlineStr">
         <is>
-          <t>31 x 31 x 23.7 cm</t>
+          <t>23.8 x 11.7 x 10.2 cm</t>
         </is>
       </c>
       <c r="BQ29" s="23" t="inlineStr">
         <is>
-          <t>31.00 x 31.00 x 23.70 cm</t>
+          <t>23.80 x 11.70 x 10.20 cm</t>
         </is>
       </c>
       <c r="BR29" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -12343,52 +12369,56 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
-        </is>
-      </c>
-      <c r="D30" s="14"/>
+          <t>B0G4RSJQVT</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Couleur: Gris</t>
+        </is>
+      </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Marque: Yaasier | Caractéristique spéciale: Lumière UV | Type de filtre: Filtre HEPA | Recommandation de surface: Tapis, Rembourrage | Source d'alimentation: Alimenté par batterie | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, coussins, canapés, tapis | Facteur de forme: Portatif | Couleur: Blanc. | Nom de modèle: 1X1BSCMY</t>
+          <t>Marque: Lubluelu | Caractéristique spéciale: Lumière UV | Type de filtre: Cartouche | Recommandation de surface: Tapis | Source d'alimentation: Câble électrique | Composants inclus: Rouleau à brosse | Sans fil ?: Non | Aspiration maximale: 18000 Millimètres | Utilisations recommandées pour le produit: matelas, canapés, tapis, linge de lit, jouets en peluche, poils d'animaux | Facteur de forme: Portatif</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99% de Tous Les acariens pour Lits, oreillers, canapés et Tapis</t>
+          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes, pour Matelas, Lits et Canapés (Gris)</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>Technologie avancée 3 en 1 : équipé d'un aspirateur anti-acariens [technologie avancée trois en un] Équipé d'un tampon de pulsation double battement et d'une lumière UV de 253,7 nm, cet aspirateur offre une grande zone de nettoyage et une efficacité accrue, idéal pour éliminer les acariens et autres allergènes de vos matelas et textiles. Avec un tampon de pulsation double Beat et 253,7 La lumière UV nm fournit cette l'aspirateur offre une grande zone de nettoyage et une efficacité accrue, idéal pour éliminer les acariens et autres allergènes de vos matelas et textiles.
-[Design sans fil léger] Maximisez votre confort avec cet aspirateur sans fil léger qui dispose d'une batterie rechargeable qui offre une autonomie allant jusqu'à 30 minutes. Son design moderne et élégant s'intègre parfaitement dans n'importe quel intérieur et rend le nettoyage sans effort.
-[Système de filtration à haute efficacité] Nettoyeur de matelas avec un filtre HEPA lavable et un filtre en coton sur la sortie, cet aspirateur capture 99,97 % des particules de poussière fine, assure un air plus sain et réduit la pollution secondaire - Idéal pour les personnes sensibles et les familles avec enfants.
-[Bac à poussière lavable et facile à nettoyer] Aspirateur anti-acariens avec le bac à poussière lavable à l'eau courante, votre aspirateur est plus facile à nettoyer. Séchez le filtre avant la réutilisation pour assurer une puissance d'aspiration optimale et des performances de nettoyage constantes.
-Polyvalence et confort d'utilisation : aspirateur anti-acariens avec lumière UV, idéal pour aspirer les poils d'animaux et les squames sur différentes surfaces en tissu telles que les matelas, les coussins, les canapés et les tapis. Profitez d'un nettoyage silencieux qui ne dérange pas les bébés ou les animaux domestiques endormis.</t>
+          <t>Aspiration puissante 18 kPa pour un nettoyage en profondeur: L’aspirateur haute performance élimine immédiatement la poussière, les saletés et les acariens profondément incrustés dans les matelas, canapés, tapis, literie et peluches. Il assure un nettoyage efficace dans chaque recoin.
+Nettoyage profond multi-étapes contre les acariens et allergènes: La combinaison d’une brosse rotative, de vibrations ultrasoniques et d’un chauffage haute température élimine efficacement les acariens et allergènes en profondeur, laissant un environnement propre et hygiénique.
+Nettoyage adapté aux personnes allergiques et respectueux des textiles: Conçu pour les foyers sensibles, le nettoyage en profondeur repose sur une technologie mécanique de battement et de chaleur sans produits chimiques. Idéal pour les personnes allergiques, les chambres d’enfants et les familles avec animaux domestiques, tout en protégeant les textiles et surfaces.
+Polyvalent pour différentes surfaces et utilisations: Convient aux matelas, canapés, tapis, literie et peluches. Il déloge la poussière et les particules incrustées et facilite l’entretien régulier des zones fortement utilisées dans la maison.
+Pratique et facile à utiliser au quotidien: Doté d’un câble extra-long de 4 mètres pour une plus grande portée et d’un design compact et léger pour une manipulation aisée. Le bac à poussière se vide rapidement et le filtre peut être séché à l’air libre après nettoyage.</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0HHRGDS1P</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -12402,13 +12432,13 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>2257594</v>
+        <v>694162</v>
       </c>
       <c r="P30" s="15">
-        <v>-17555</v>
+        <v>-76398</v>
       </c>
       <c r="Q30" s="16">
-        <v>-0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="R30" s="17" t="inlineStr">
         <is>
@@ -12417,7 +12447,7 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T30" s="15"/>
@@ -12429,37 +12459,37 @@
         <v>1</v>
       </c>
       <c r="Z30" s="20">
-        <v>28.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA30" s="4"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AE30" s="15">
         <v>0</v>
       </c>
       <c r="AF30" s="21">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
       </c>
       <c r="AH30" s="20">
-        <v>5.98</v>
+        <v>8.11</v>
       </c>
       <c r="AI30" s="16">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AL30" s="19">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AM30" s="13" t="inlineStr">
         <is>
@@ -12470,14 +12500,14 @@
       <c r="AO30" s="13"/>
       <c r="AP30" s="4"/>
       <c r="AQ30" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR30" s="19">
         <v>1</v>
       </c>
       <c r="AS30" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT30" s="13" t="inlineStr">
@@ -12485,21 +12515,9 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU30" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV30" s="14" t="inlineStr">
-        <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
-        </is>
-      </c>
-      <c r="AW30" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
-        </is>
-      </c>
+      <c r="AU30" s="13"/>
+      <c r="AV30" s="14"/>
+      <c r="AW30" s="13"/>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13"/>
       <c r="AZ30" s="13"/>
@@ -12518,43 +12536,43 @@
       <c r="BI30" s="23"/>
       <c r="BJ30" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2,33 Kilograms</t>
         </is>
       </c>
       <c r="BK30" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H centimètres</t>
+          <t>30L x 24,5l x 23H centimètres</t>
         </is>
       </c>
       <c r="BM30" s="23"/>
       <c r="BN30" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="BO30" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="BP30" s="23" t="inlineStr">
         <is>
-          <t>23.8 x 11.7 x 10.2 cm</t>
+          <t>33.6 x 26.9 x 25.6 cm</t>
         </is>
       </c>
       <c r="BQ30" s="23" t="inlineStr">
         <is>
-          <t>23.80 x 11.70 x 10.20 cm</t>
+          <t>33.60 x 26.90 x 25.60 cm</t>
         </is>
       </c>
       <c r="BR30" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -12565,56 +12583,52 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Couleur: Gris</t>
-        </is>
-      </c>
+          <t>B0GF7CNTYL</t>
+        </is>
+      </c>
+      <c r="D31" s="14"/>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Marque: Lubluelu | Caractéristique spéciale: Lumière UV | Type de filtre: Cartouche | Recommandation de surface: Tapis | Source d'alimentation: Câble électrique | Composants inclus: Rouleau à brosse | Sans fil ?: Non | Aspiration maximale: 18000 Millimètres | Utilisations recommandées pour le produit: matelas, canapés, tapis, linge de lit, jouets en peluche, poils d'animaux | Facteur de forme: Portatif</t>
+          <t>Marque: Liwankaqi | Caractéristique spéciale: Lumière UV | Recommandation de surface: Matelas | Source d'alimentation: Batterie intégrée | Composants inclus: Aspirateur anti-acariens | Sans fil ?: Oui | Poids de l'article: 1300 Grammes | Capacité: 200 ml | Utilisations recommandées pour le produit: Matelas, oreillers, canapés en tissu, housses de couette | Facteur de forme: Portatif</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes, pour Matelas, Lits et Canapés (Gris)</t>
+          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et Canapé</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>Aspiration puissante 18 kPa pour un nettoyage en profondeur: L’aspirateur haute performance élimine immédiatement la poussière, les saletés et les acariens profondément incrustés dans les matelas, canapés, tapis, literie et peluches. Il assure un nettoyage efficace dans chaque recoin.
-Nettoyage profond multi-étapes contre les acariens et allergènes: La combinaison d’une brosse rotative, de vibrations ultrasoniques et d’un chauffage haute température élimine efficacement les acariens et allergènes en profondeur, laissant un environnement propre et hygiénique.
-Nettoyage adapté aux personnes allergiques et respectueux des textiles: Conçu pour les foyers sensibles, le nettoyage en profondeur repose sur une technologie mécanique de battement et de chaleur sans produits chimiques. Idéal pour les personnes allergiques, les chambres d’enfants et les familles avec animaux domestiques, tout en protégeant les textiles et surfaces.
-Polyvalent pour différentes surfaces et utilisations: Convient aux matelas, canapés, tapis, literie et peluches. Il déloge la poussière et les particules incrustées et facilite l’entretien régulier des zones fortement utilisées dans la maison.
-Pratique et facile à utiliser au quotidien: Doté d’un câble extra-long de 4 mètres pour une plus grande portée et d’un design compact et léger pour une manipulation aisée. Le bac à poussière se vide rapidement et le filtre peut être séché à l’air libre après nettoyage.</t>
+          <t>Forte aspiration grâce aux vibrations et à la technologie d'aspiration : notre aspirateur anti-acariens pour matelas utilise les vibrations et une forte aspiration. Cet appareil de nettoyage de matelas avec double coussin pliable nettoie en profondeur – un véritable vainqueur du test.
+Travail sans fil avec batterie intégrée : ce nettoyeur anti-acariens sans fil avec batterie offre une longue durée de vie. L'appareil de nettoyage pour matelas permet un mouvement libre sans câble.
+Ultrasons et lumière UV pour un nettoyage hygiénique en profondeur : l'aspirateur anti-acariens inhibe les acariens par ultrasons. Cet aspirateur de matelas avec lumière UV nettoie plus profondément qu'un matelas à vapeur.
+Système de filtration efficace contre le retour de la poussière : l'aspirateur anti-acariens a un système de filtration scellé. Ce nettoyeur de lit empêche le retour de la poussière et la saleté secondaire.
+Composants amovibles et lavables pour le nettoyage : l'aspirateur anti-acariens ergonomique a des pièces amovibles. Ce nettoyeur sous vide Mattress est facile à nettoyer pour une performance durable.</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0HHRGDS1P</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -12628,13 +12642,11 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>694162</v>
-      </c>
-      <c r="P31" s="15">
-        <v>-76398</v>
-      </c>
+        <v>1830159</v>
+      </c>
+      <c r="P31" s="15"/>
       <c r="Q31" s="16">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
@@ -12643,7 +12655,7 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T31" s="15"/>
@@ -12654,39 +12666,27 @@
       <c r="Y31" s="19">
         <v>1</v>
       </c>
-      <c r="Z31" s="20">
-        <v>99.99</v>
-      </c>
+      <c r="Z31" s="20"/>
       <c r="AA31" s="4"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>26</v>
-      </c>
-      <c r="AE31" s="15">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE31" s="15"/>
       <c r="AF31" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
       </c>
-      <c r="AH31" s="20">
-        <v>8.11</v>
-      </c>
+      <c r="AH31" s="20"/>
       <c r="AI31" s="16">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="AJ31"/>
-      <c r="AK31" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AL31" s="19">
-        <v>288</v>
-      </c>
+      <c r="AK31" s="13"/>
+      <c r="AL31" s="19"/>
       <c r="AM31" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12695,17 +12695,9 @@
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31" s="4"/>
-      <c r="AQ31" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR31" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS31" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="AQ31" s="19"/>
+      <c r="AR31" s="19"/>
+      <c r="AS31" s="14"/>
       <c r="AT31" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12719,58 +12711,38 @@
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
-      <c r="BC31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC31" s="13"/>
       <c r="BD31" s="13"/>
       <c r="BE31" s="13"/>
-      <c r="BF31" s="13"/>
+      <c r="BF31" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
       <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>2,33 Kilograms</t>
+          <t>1300 Grammes</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>30L x 24,5l x 23H centimètres</t>
+          <t>28L x 27l x 11H centimètres</t>
         </is>
       </c>
       <c r="BM31" s="23"/>
-      <c r="BN31" s="23" t="inlineStr">
-        <is>
-          <t>2.33 kg</t>
-        </is>
-      </c>
-      <c r="BO31" s="23" t="inlineStr">
-        <is>
-          <t>2.33 kg</t>
-        </is>
-      </c>
-      <c r="BP31" s="23" t="inlineStr">
-        <is>
-          <t>33.6 x 26.9 x 25.6 cm</t>
-        </is>
-      </c>
-      <c r="BQ31" s="23" t="inlineStr">
-        <is>
-          <t>33.60 x 26.90 x 25.60 cm</t>
-        </is>
-      </c>
-      <c r="BR31" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN31" s="23"/>
+      <c r="BO31" s="23"/>
+      <c r="BP31" s="23"/>
+      <c r="BQ31" s="23"/>
+      <c r="BR31" s="13"/>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
@@ -12779,52 +12751,52 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Marque: Liwankaqi | Caractéristique spéciale: Lumière UV | Recommandation de surface: Matelas | Source d'alimentation: Batterie intégrée | Composants inclus: Aspirateur anti-acariens | Sans fil ?: Oui | Poids de l'article: 1300 Grammes | Capacité: 200 ml | Utilisations recommandées pour le produit: Matelas, oreillers, canapés en tissu, housses de couette | Facteur de forme: Portatif</t>
+          <t>Marque: Ubric | Caractéristique spéciale: Sans fil | Type de filtre: Filtre HEPA | Recommandation de surface: Canapé, Coussin, Matelas, Tapis | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, canapés, coussins, tapis, surfaces en tissu | Facteur de forme: Portatif | Fabricant: Ubric | Nombre d'articles: 1</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et Canapé</t>
+          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapis (blanc)</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>Forte aspiration grâce aux vibrations et à la technologie d'aspiration : notre aspirateur anti-acariens pour matelas utilise les vibrations et une forte aspiration. Cet appareil de nettoyage de matelas avec double coussin pliable nettoie en profondeur – un véritable vainqueur du test.
-Travail sans fil avec batterie intégrée : ce nettoyeur anti-acariens sans fil avec batterie offre une longue durée de vie. L'appareil de nettoyage pour matelas permet un mouvement libre sans câble.
-Ultrasons et lumière UV pour un nettoyage hygiénique en profondeur : l'aspirateur anti-acariens inhibe les acariens par ultrasons. Cet aspirateur de matelas avec lumière UV nettoie plus profondément qu'un matelas à vapeur.
-Système de filtration efficace contre le retour de la poussière : l'aspirateur anti-acariens a un système de filtration scellé. Ce nettoyeur de lit empêche le retour de la poussière et la saleté secondaire.
-Composants amovibles et lavables pour le nettoyage : l'aspirateur anti-acariens ergonomique a des pièces amovibles. Ce nettoyeur sous vide Mattress est facile à nettoyer pour une performance durable.</t>
+          <t>Profitez de la liberté du nettoyage sans fil. La batterie rechargeable offre une longue durée de vie de 20 minutes.
+Libérez-vous des câbles avec cet aspirateur entièrement sans fil qui offre des possibilités de nettoyage illimitées pour enlever la poussière et la saleté sur les matelas, canapés, coussins et tapis n'importe où.
+Il dispose d'un moteur puissant et d'un filtre HEPA de haute qualité qui capture efficacement les acariens microscopiques, les poils d'animaux, le pollen et autres particules de poussière fine, améliorant considérablement la qualité de l'air dans votre maison.
+Spécialement conçue pour les surfaces en tissu, la tête d'aspiration spéciale nettoie en douceur et en profondeur dans les fibres du matelas et les rembourrages rafraîchissent votre literie et vos meubles.
+La batterie d'aspirateur anti-acariens peut facilement absorber les poils d'animaux et les squames, etc. Convient pour les surfaces en tissu : matelas, draps, oreillers, tapis, canapés en tissu, etc. Le design silencieux ne dérangera pas les bébés ou les animaux domestiques endormis.</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -12838,7 +12810,7 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>1830159</v>
+        <v>985017</v>
       </c>
       <c r="P32" s="15"/>
       <c r="Q32" s="16">
@@ -12851,7 +12823,7 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T32" s="15"/>
@@ -12862,27 +12834,39 @@
       <c r="Y32" s="19">
         <v>1</v>
       </c>
-      <c r="Z32" s="20"/>
+      <c r="Z32" s="20">
+        <v>20.99</v>
+      </c>
       <c r="AA32" s="4"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="AE32" s="15">
+        <v>0</v>
+      </c>
       <c r="AF32" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
-      <c r="AH32" s="20"/>
+      <c r="AH32" s="20">
+        <v>6.29</v>
+      </c>
       <c r="AI32" s="16">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AJ32"/>
-      <c r="AK32" s="13"/>
-      <c r="AL32" s="19"/>
+      <c r="AK32" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AL32" s="19">
+        <v>194</v>
+      </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12892,16 +12876,34 @@
       <c r="AO32" s="13"/>
       <c r="AP32" s="4"/>
       <c r="AQ32" s="19"/>
-      <c r="AR32" s="19"/>
-      <c r="AS32" s="14"/>
+      <c r="AR32" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS32" s="14" t="inlineStr">
+        <is>
+          <t>Ubric</t>
+        </is>
+      </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU32" s="13"/>
-      <c r="AV32" s="14"/>
-      <c r="AW32" s="13"/>
+      <c r="AU32" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV32" s="14" t="inlineStr">
+        <is>
+          <t>MONGKOK KOWLOON 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42</t>
+        </is>
+      </c>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13"/>
       <c r="AZ32" s="13"/>
@@ -12910,35 +12912,47 @@
       <c r="BC32" s="13"/>
       <c r="BD32" s="13"/>
       <c r="BE32" s="13"/>
-      <c r="BF32" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF32" s="13"/>
       <c r="BG32" s="13"/>
       <c r="BH32" s="14"/>
       <c r="BI32" s="23"/>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>1300 Grammes</t>
+          <t>410 g</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
-        </is>
-      </c>
-      <c r="BL32" s="23" t="inlineStr">
-        <is>
-          <t>28L x 27l x 11H centimètres</t>
-        </is>
-      </c>
+          <t>410.00 g</t>
+        </is>
+      </c>
+      <c r="BL32" s="23"/>
       <c r="BM32" s="23"/>
-      <c r="BN32" s="23"/>
-      <c r="BO32" s="23"/>
-      <c r="BP32" s="23"/>
-      <c r="BQ32" s="23"/>
-      <c r="BR32" s="13"/>
+      <c r="BN32" s="23" t="inlineStr">
+        <is>
+          <t>410 g</t>
+        </is>
+      </c>
+      <c r="BO32" s="23" t="inlineStr">
+        <is>
+          <t>410.00 g</t>
+        </is>
+      </c>
+      <c r="BP32" s="23" t="inlineStr">
+        <is>
+          <t>34.8 x 24.7 x 10.6 cm</t>
+        </is>
+      </c>
+      <c r="BQ32" s="23" t="inlineStr">
+        <is>
+          <t>34.80 x 24.70 x 10.60 cm</t>
+        </is>
+      </c>
+      <c r="BR32" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -12947,52 +12961,56 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
-        </is>
-      </c>
-      <c r="D33" s="14"/>
+          <t>B0GMPVWCZM</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Couleur: Lilas</t>
+        </is>
+      </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Marque: Ubric | Caractéristique spéciale: Sans fil | Type de filtre: Filtre HEPA | Recommandation de surface: Canapé, Coussin, Matelas, Tapis | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, canapés, coussins, tapis, surfaces en tissu | Facteur de forme: Portatif | Fabricant: Ubric | Nombre d'articles: 1</t>
+          <t>Marque: Elecbee | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, canapés, moquettes | Facteur de forme: Portatif | Couleur: Lilas | Dimensions du produit: 20L x 30l x 20H centimètres | Fabricant: Elecbee | Nombre d'articles: 1</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>Elecbee</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric</t>
+          <t>https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapis (blanc)</t>
+          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie ultrasonique, aspirateur à main pour matelas, canapé, moquette</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>Profitez de la liberté du nettoyage sans fil. La batterie rechargeable offre une longue durée de vie de 20 minutes.
-Libérez-vous des câbles avec cet aspirateur entièrement sans fil qui offre des possibilités de nettoyage illimitées pour enlever la poussière et la saleté sur les matelas, canapés, coussins et tapis n'importe où.
-Il dispose d'un moteur puissant et d'un filtre HEPA de haute qualité qui capture efficacement les acariens microscopiques, les poils d'animaux, le pollen et autres particules de poussière fine, améliorant considérablement la qualité de l'air dans votre maison.
-Spécialement conçue pour les surfaces en tissu, la tête d'aspiration spéciale nettoie en douceur et en profondeur dans les fibres du matelas et les rembourrages rafraîchissent votre literie et vos meubles.
-La batterie d'aspirateur anti-acariens peut facilement absorber les poils d'animaux et les squames, etc. Convient pour les surfaces en tissu : matelas, draps, oreillers, tapis, canapés en tissu, etc. Le design silencieux ne dérangera pas les bébés ou les animaux domestiques endormis.</t>
+          <t>18 000 frappes à haute fréquence par minute : le design de secouement semblable à la main extrait profondément les carcasses d'acariens et les pellicules de la peau.
+Aspiration de 13 000 Pa : une forte aspiration apporte la saleté à la surface et la élimine immédiatement. Vous offre un nettoyage en profondeur et efficace.
+Double stérilisation UV + ultrasonique : la technologie de stérilisation UV nettoie en profondeur, inactive les acariens, les ultrasons inhibent la multiplication, la puissance d'aspiration et de nettoyage est supérieure à 99 %.
+【Nettoyage intelligent à quatre modes 】 Demite/ultrasonique/brosse à rouleaux/stérilisation UV, quatre modes sont commutés avec un bouton, et l'écran LED est clairement affiché.
+Design sans fil : l'aspirateur anti-acariens a un design sans fil, charge rapide de type C, se débarrasser des prises et des câbles, canapé/matelas disponible n'importe où.</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0HJRR2QDH</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -13006,7 +13024,7 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>985017</v>
+        <v>933257</v>
       </c>
       <c r="P33" s="15"/>
       <c r="Q33" s="16">
@@ -13019,7 +13037,7 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T33" s="15"/>
@@ -13031,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>20.99</v>
+        <v>75.99</v>
       </c>
       <c r="AA33" s="4"/>
       <c r="AB33" s="1"/>
@@ -13043,25 +13061,25 @@
         <v>0</v>
       </c>
       <c r="AF33" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
       <c r="AH33" s="20">
-        <v>6.29</v>
+        <v>7.29</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>194</v>
+        <v>141</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -13071,13 +13089,15 @@
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33" s="4"/>
-      <c r="AQ33" s="19"/>
+      <c r="AQ33" s="19">
+        <v>9</v>
+      </c>
       <c r="AR33" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
@@ -13087,17 +13107,17 @@
       </c>
       <c r="AU33" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV33" s="14" t="inlineStr">
         <is>
-          <t>MONGKOK KOWLOON 999077 HK</t>
+          <t>武汉市 洪山区 湖北省 430070 CN</t>
         </is>
       </c>
       <c r="AW33" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
         </is>
       </c>
       <c r="AX33" s="13"/>
@@ -13105,7 +13125,11 @@
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
-      <c r="BC33" s="13"/>
+      <c r="BC33" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD33" s="13"/>
       <c r="BE33" s="13"/>
       <c r="BF33" s="13"/>
@@ -13114,39 +13138,43 @@
       <c r="BI33" s="23"/>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>410 g</t>
+          <t>2 Kilograms</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>410.00 g</t>
-        </is>
-      </c>
-      <c r="BL33" s="23"/>
+          <t>2.00 kg</t>
+        </is>
+      </c>
+      <c r="BL33" s="23" t="inlineStr">
+        <is>
+          <t>20L x 30l x 20H centimètres</t>
+        </is>
+      </c>
       <c r="BM33" s="23"/>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>410 g</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>410.00 g</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>34.8 x 24.7 x 10.6 cm</t>
+          <t>32 x 21 x 21 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>34.80 x 24.70 x 10.60 cm</t>
+          <t>32.00 x 21.00 x 21.00 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13185,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -13167,46 +13195,46 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Marque: Elecbee | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Sans fil ?: Oui | Utilisations recommandées pour le produit: Matelas, canapés, moquettes | Facteur de forme: Portatif | Couleur: Lilas | Dimensions du produit: 20L x 30l x 20H centimètres | Fabricant: Elecbee | Nombre d'articles: 1</t>
+          <t>Marque: XINYUDAILY | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Sans fil ?: Oui | Capacité: 520 ml | Utilisations recommandées pour le produit: Matelas, canapés, coussins, tapis, sièges de voiture et autres textiles | Facteur de forme: Portatif | Couleur: Lilas | Dimensions du produit: 32L x 29l x 21H centimètres | Fabricant: Wenzhou Laipin Electronic Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Elecbee</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee</t>
+          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie ultrasonique, aspirateur à main pour matelas, canapé, moquette</t>
+          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, aspirateur pour matelas pour éliminer les acariens, les allergènes et les</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>18 000 frappes à haute fréquence par minute : le design de secouement semblable à la main extrait profondément les carcasses d'acariens et les pellicules de la peau.
-Aspiration de 13 000 Pa : une forte aspiration apporte la saleté à la surface et la élimine immédiatement. Vous offre un nettoyage en profondeur et efficace.
-Double stérilisation UV + ultrasonique : la technologie de stérilisation UV nettoie en profondeur, inactive les acariens, les ultrasons inhibent la multiplication, la puissance d'aspiration et de nettoyage est supérieure à 99 %.
-【Nettoyage intelligent à quatre modes 】 Demite/ultrasonique/brosse à rouleaux/stérilisation UV, quatre modes sont commutés avec un bouton, et l'écran LED est clairement affiché.
-Design sans fil : l'aspirateur anti-acariens a un design sans fil, charge rapide de type C, se débarrasser des prises et des câbles, canapé/matelas disponible n'importe où.</t>
+          <t>Nettoyage en profondeur efficace 4 en 1 : notre nettoyeur de matelas sans fil combine 4 technologies avancées : puissance d'aspiration puissante de 13 kPa, un rouleau à brosse de 18 000 coups/min, lumière UV-C de 253,7 nm pour la stérilisation et les ultrasons. Il élimine facilement la saleté incrustée, les acariens, les allergènes et les bactéries des matelas, literie, canapés et coussins. Créez un environnement de sommeil propre et plus sain pour votre famille.
+Double tasse et système de filtration multi-niveaux : la conception bien pensée avec deux bacs à poussière séparés (520 ml) sépare efficacement la poussière et les déchets de l'air, ce qui est non seulement plus hygiénique, mais garantit également une puissance d'aspiration élevée et constante. En combinaison avec le système de filtration multicouche, 99,99 % des particules les plus fines sont retenues de manière fiable - Idéal pour les personnes allergiques.
+Affichage LED et liberté sans fil : quatre modes de nettoyage (aspiration/ultrasons/rouleau à brosse/lumière UV-C) peuvent être facilement changés en appuyant sur un bouton, clairement lisibles sur l'écran LED. Le design léger et sans fil offre une liberté de mouvement maximale. La puissante batterie offre jusqu'à 35 minutes d'autonomie en mode Eco et 20 minutes en mode boost, assez pour nettoyer en profondeur la chambre et le salon.
+Léger, compact et polyvalent : grâce à son faible poids et à sa forme compacte, cet aspirateur à main tient parfaitement dans la main. Il nettoie sans effort non seulement les matelas et les canapés, mais aussi les tapis, les coussins, les sièges de voiture et autres textiles.
+Cadeau bien pensé : ce nettoyeur de matelas n'est pas seulement un appareil ménager pratique, mais aussi une idée cadeau idéale pour vos proches, emballé dans une boîte cadeau attrayante.</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0HJRR2QDH</t>
+          <t>B0GXBVPPWQ</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -13220,11 +13248,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>933257</v>
-      </c>
-      <c r="P34" s="15"/>
+        <v>358987</v>
+      </c>
+      <c r="P34" s="15">
+        <v>719726</v>
+      </c>
       <c r="Q34" s="16">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -13233,7 +13263,7 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T34" s="15"/>
@@ -13245,7 +13275,7 @@
         <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>75.99</v>
+        <v>69.99</v>
       </c>
       <c r="AA34" s="4"/>
       <c r="AB34" s="1"/>
@@ -13257,25 +13287,25 @@
         <v>0</v>
       </c>
       <c r="AF34" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
       <c r="AH34" s="20">
-        <v>7.29</v>
+        <v>8.03</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
@@ -13286,14 +13316,14 @@
       <c r="AO34" s="13"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR34" s="19">
         <v>1</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>XINYU-EU</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -13308,12 +13338,12 @@
       </c>
       <c r="AV34" s="14" t="inlineStr">
         <is>
-          <t>武汉市 洪山区 湖北省 430070 CN</t>
+          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
         </is>
       </c>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
@@ -13321,12 +13351,12 @@
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
-      <c r="BC34" s="13" t="inlineStr">
+      <c r="BC34" s="13"/>
+      <c r="BD34" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="13"/>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
@@ -13334,38 +13364,38 @@
       <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>2 Kilograms</t>
+          <t>2,2 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>2.20 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>20L x 30l x 20H centimètres</t>
+          <t>32L x 29l x 21H centimètres</t>
         </is>
       </c>
       <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>2 kg</t>
+          <t>2.2 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>2.20 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>32 x 21 x 21 cm</t>
+          <t>32 x 29 x 21 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>32.00 x 21.00 x 21.00 cm</t>
+          <t>32.00 x 29.00 x 21.00 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
@@ -13381,56 +13411,52 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Couleur: Lilas</t>
-        </is>
-      </c>
+          <t>B0GWH1FGJB</t>
+        </is>
+      </c>
+      <c r="D35" s="14"/>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>Marque: XINYUDAILY | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Sans fil ?: Oui | Capacité: 520 ml | Utilisations recommandées pour le produit: Matelas, canapés, coussins, tapis, sièges de voiture et autres textiles | Facteur de forme: Portatif | Couleur: Lilas | Dimensions du produit: 32L x 29l x 21H centimètres | Fabricant: Wenzhou Laipin Electronic Technology Co., Ltd.</t>
+          <t>Marque: Timisea | Caractéristique spéciale: Stérilisation à la lumière bleue | Recommandation de surface: Rembourrage | Source d'alimentation: Alimenté par batterie | Composants inclus: Buse large ; embout suceur plat ; embout brosse | Sans fil ?: Oui | Utilisations recommandées pour le produit: matelas, meubles rembourrés, tapis, intérieurs de voiture | Facteur de forme: Portatif | Couleur: Blanc. | Dimensions du produit: 21L x 8l x 37H centimètres</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>XINYUDAILY</t>
+          <t>Timisea</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
+          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, aspirateur pour matelas pour éliminer les acariens, les allergènes et les</t>
+          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas pour la maison et la voiture, élimine 99,9 % des acariens</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>Nettoyage en profondeur efficace 4 en 1 : notre nettoyeur de matelas sans fil combine 4 technologies avancées : puissance d'aspiration puissante de 13 kPa, un rouleau à brosse de 18 000 coups/min, lumière UV-C de 253,7 nm pour la stérilisation et les ultrasons. Il élimine facilement la saleté incrustée, les acariens, les allergènes et les bactéries des matelas, literie, canapés et coussins. Créez un environnement de sommeil propre et plus sain pour votre famille.
-Double tasse et système de filtration multi-niveaux : la conception bien pensée avec deux bacs à poussière séparés (520 ml) sépare efficacement la poussière et les déchets de l'air, ce qui est non seulement plus hygiénique, mais garantit également une puissance d'aspiration élevée et constante. En combinaison avec le système de filtration multicouche, 99,99 % des particules les plus fines sont retenues de manière fiable - Idéal pour les personnes allergiques.
-Affichage LED et liberté sans fil : quatre modes de nettoyage (aspiration/ultrasons/rouleau à brosse/lumière UV-C) peuvent être facilement changés en appuyant sur un bouton, clairement lisibles sur l'écran LED. Le design léger et sans fil offre une liberté de mouvement maximale. La puissante batterie offre jusqu'à 35 minutes d'autonomie en mode Eco et 20 minutes en mode boost, assez pour nettoyer en profondeur la chambre et le salon.
-Léger, compact et polyvalent : grâce à son faible poids et à sa forme compacte, cet aspirateur à main tient parfaitement dans la main. Il nettoie sans effort non seulement les matelas et les canapés, mais aussi les tapis, les coussins, les sièges de voiture et autres textiles.
-Cadeau bien pensé : ce nettoyeur de matelas n'est pas seulement un appareil ménager pratique, mais aussi une idée cadeau idéale pour vos proches, emballé dans une boîte cadeau attrayante.</t>
+          <t>Aspirateur et aspirateur anti-acariens 2 en 1 pour un nettoyage en profondeur : cet aspirateur anti-acariens polyvalent combine les fonctions d'un aspirateur puissant et d'un aspirateur de matelas spécialisé en un seul appareil. Avec une puissance d'aspiration de 8000 PA et une puissance moteur de 100 W, il élimine efficacement la poussière, les miettes, les cheveux, les acariens et leurs allergènes des matelas, des meubles rembourrés, des tapis et des sièges de voiture. La technologie brevetée 2 en 1 permet à la fois le nettoyage quotidien de l'aspirateur et l'élimination spéciale des acariens, parfait pour les personnes allergiques et les ménages ayant des normes d'hygiène élevées.
+Élimination professionnelle des acariens avec stérilisation à lumière bleue et frappe à haute fréquence : l'aspirateur anti-acariens dispose d'une fonction de stérilisation à lumière bleue intégrée qui tue efficacement les bactéries et les acariens sur les surfaces. La fonction de frappe haute fréquence élimine les acariens profonds, les œufs et les allergènes des textiles, tandis que le courant d'aspiration puissant de 8000 PA les aspire immédiatement. Avec une force de pénétration de 30 cm, il nettoie même les couettes d'hiver épaisses et les matelas jusqu'à les couches les plus profondes – Idéal pour le nettoyage des matelas et l'entretien du rembourrage.
+Trois embouts spécialisés pour des solutions de nettoyage complètes : trois embouts fonctionnels sont inclus dans la livraison : un embout de buse large pour matelas et grandes surfaces, un embout suceur plat pour l'intérieur de voiture et des fentes étroites, ainsi qu'un embout brosse pour meubles rembourrés et tapis. Cette combinaison fait de l'aspirateur anti-acariens le compagnon idéal pour le nettoyage domestique, l'entretien de la voiture, l'hygiène de l'hôtel et les activités de plein air – un appareil pour tous les besoins de nettoyage.
+Technologie puissante avec design pratique : l'aspirateur anti-acariens pratique convainc par une autonomie de la batterie pour jusqu'à 150 m² de surface de nettoyage par charge et un bac à poussière transparent et lavable. Le design ergonomique avec poignée confortable permet un travail sans fatigue, tandis que le bruit de fonctionnement silencieux de moins de 70 dB garantit une utilisation sans interférences. L'utilisation à un bouton et le refroidissement optimisé garantissent une manipulation facile et une longue durée de vie.
+Avantages pour la santé et domaines d'application : l'utilisation régulière de cet aspirateur à matelas réduit la charge aux acariens jusqu'à 99,9 %, ce qui est particulièrement bénéfique pour les personnes allergiques, les asthmatiques et les familles avec enfants. Idéal pour le nettoyage des matelas, entretien des canapés et des coussins, nettoyage intérieur de voiture, hygiène de tapis, lits d'hôtel, chambres d'enfants et ménages de propriétaires d'animaux. Créez une maison hygiénique propre sans acariens, allergènes et bactéries.</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GXBVPPWQ</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -13444,13 +13470,11 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>358987</v>
-      </c>
-      <c r="P35" s="15">
-        <v>719726</v>
-      </c>
+        <v>506923</v>
+      </c>
+      <c r="P35" s="15"/>
       <c r="Q35" s="16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -13459,7 +13483,7 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T35" s="15"/>
@@ -13471,37 +13495,31 @@
         <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>69.99</v>
+        <v>35.99</v>
       </c>
       <c r="AA35" s="4"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="2"/>
-      <c r="AD35" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE35" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="21">
-        <v>4</v>
-      </c>
+      <c r="AD35" s="19"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="21"/>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
       <c r="AH35" s="20">
-        <v>8.03</v>
+        <v>6.06</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -13511,15 +13529,13 @@
       <c r="AN35" s="13"/>
       <c r="AO35" s="13"/>
       <c r="AP35" s="4"/>
-      <c r="AQ35" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ35" s="19"/>
       <c r="AR35" s="19">
         <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Alloplectus</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -13534,12 +13550,12 @@
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
+          <t>金华市 浙江省 322215 CN</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
@@ -13548,11 +13564,7 @@
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
       <c r="BC35" s="13"/>
-      <c r="BD35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD35" s="13"/>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
@@ -13560,43 +13572,43 @@
       <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>2,2 Kilograms</t>
+          <t>855 g</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>855.00 g</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>32L x 29l x 21H centimètres</t>
+          <t>21L x 8l x 37H centimètres</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>2.2 kg</t>
+          <t>855 g</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>855.00 g</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>32 x 29 x 21 cm</t>
+          <t>33 x 21 x 8 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>32.00 x 29.00 x 21.00 cm</t>
+          <t>33.00 x 21.00 x 8.00 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -13607,52 +13619,48 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Marque: Timisea | Caractéristique spéciale: Stérilisation à la lumière bleue | Recommandation de surface: Rembourrage | Source d'alimentation: Alimenté par batterie | Composants inclus: Buse large ; embout suceur plat ; embout brosse | Sans fil ?: Oui | Utilisations recommandées pour le produit: matelas, meubles rembourrés, tapis, intérieurs de voiture | Facteur de forme: Portatif | Couleur: Blanc. | Dimensions du produit: 21L x 8l x 37H centimètres</t>
+          <t>Marque: ALLILUYAA | Caractéristique spéciale: Triple filtration | Recommandation de surface: Matelas | Composants inclus: Filtre lavable | Sans fil ?: Oui | Aspiration maximale: 10000 Millimètres | Utilisations recommandées pour le produit: matelas, canapés, couvertures, vêtements, peluches et lits pour animaux de compagnie | Facteur de forme: Portatif | Couleur: Blanc | Dimensions du produit: 10L x 10l x 10H millimètres</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Timisea</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
+          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas pour la maison et la voiture, élimine 99,9 % des acariens</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés, Matelas Et Jouets en Peluche</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur et aspirateur anti-acariens 2 en 1 pour un nettoyage en profondeur : cet aspirateur anti-acariens polyvalent combine les fonctions d'un aspirateur puissant et d'un aspirateur de matelas spécialisé en un seul appareil. Avec une puissance d'aspiration de 8000 PA et une puissance moteur de 100 W, il élimine efficacement la poussière, les miettes, les cheveux, les acariens et leurs allergènes des matelas, des meubles rembourrés, des tapis et des sièges de voiture. La technologie brevetée 2 en 1 permet à la fois le nettoyage quotidien de l'aspirateur et l'élimination spéciale des acariens, parfait pour les personnes allergiques et les ménages ayant des normes d'hygiène élevées.
-Élimination professionnelle des acariens avec stérilisation à lumière bleue et frappe à haute fréquence : l'aspirateur anti-acariens dispose d'une fonction de stérilisation à lumière bleue intégrée qui tue efficacement les bactéries et les acariens sur les surfaces. La fonction de frappe haute fréquence élimine les acariens profonds, les œufs et les allergènes des textiles, tandis que le courant d'aspiration puissant de 8000 PA les aspire immédiatement. Avec une force de pénétration de 30 cm, il nettoie même les couettes d'hiver épaisses et les matelas jusqu'à les couches les plus profondes – Idéal pour le nettoyage des matelas et l'entretien du rembourrage.
-Trois embouts spécialisés pour des solutions de nettoyage complètes : trois embouts fonctionnels sont inclus dans la livraison : un embout de buse large pour matelas et grandes surfaces, un embout suceur plat pour l'intérieur de voiture et des fentes étroites, ainsi qu'un embout brosse pour meubles rembourrés et tapis. Cette combinaison fait de l'aspirateur anti-acariens le compagnon idéal pour le nettoyage domestique, l'entretien de la voiture, l'hygiène de l'hôtel et les activités de plein air – un appareil pour tous les besoins de nettoyage.
-Technologie puissante avec design pratique : l'aspirateur anti-acariens pratique convainc par une autonomie de la batterie pour jusqu'à 150 m² de surface de nettoyage par charge et un bac à poussière transparent et lavable. Le design ergonomique avec poignée confortable permet un travail sans fatigue, tandis que le bruit de fonctionnement silencieux de moins de 70 dB garantit une utilisation sans interférences. L'utilisation à un bouton et le refroidissement optimisé garantissent une manipulation facile et une longue durée de vie.
-Avantages pour la santé et domaines d'application : l'utilisation régulière de cet aspirateur à matelas réduit la charge aux acariens jusqu'à 99,9 %, ce qui est particulièrement bénéfique pour les personnes allergiques, les asthmatiques et les familles avec enfants. Idéal pour le nettoyage des matelas, entretien des canapés et des coussins, nettoyage intérieur de voiture, hygiène de tapis, lits d'hôtel, chambres d'enfants et ménages de propriétaires d'animaux. Créez une maison hygiénique propre sans acariens, allergènes et bactéries.</t>
+          <t>1 pièce</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -13666,11 +13674,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>506923</v>
-      </c>
-      <c r="P36" s="15"/>
+        <v>1103214</v>
+      </c>
+      <c r="P36" s="15">
+        <v>-21169</v>
+      </c>
       <c r="Q36" s="16">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -13679,7 +13689,7 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T36" s="15"/>
@@ -13691,14 +13701,20 @@
         <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>35.99</v>
+        <v>25.99</v>
       </c>
       <c r="AA36" s="4"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="2"/>
-      <c r="AD36" s="19"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="21"/>
+      <c r="AD36" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE36" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="21">
+        <v>1</v>
+      </c>
       <c r="AG36" s="22">
         <v>0</v>
       </c>
@@ -13706,16 +13722,16 @@
         <v>6.06</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
@@ -13725,13 +13741,15 @@
       <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
       <c r="AP36" s="4"/>
-      <c r="AQ36" s="19"/>
+      <c r="AQ36" s="19">
+        <v>7</v>
+      </c>
       <c r="AR36" s="19">
         <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Alloplectus</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
@@ -13746,12 +13764,12 @@
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>金华市 浙江省 322215 CN</t>
+          <t>bayuquan LiaoNing 115007 CN</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
@@ -13768,38 +13786,38 @@
       <c r="BI36" s="23"/>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>855 g</t>
+          <t>430 g</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>855.00 g</t>
+          <t>430.00 g</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>21L x 8l x 37H centimètres</t>
+          <t>10L x 10l x 10H millimètres</t>
         </is>
       </c>
       <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>855 g</t>
+          <t>430 g</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>855.00 g</t>
+          <t>430.00 g</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>33 x 21 x 8 cm</t>
+          <t>25.1 x 20.5 x 11.2 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>33.00 x 21.00 x 8.00 cm</t>
+          <t>25.10 x 20.50 x 11.20 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -13815,48 +13833,52 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>Marque: ALLILUYAA | Caractéristique spéciale: Triple filtration | Recommandation de surface: Matelas | Composants inclus: Filtre lavable | Sans fil ?: Oui | Aspiration maximale: 10000 Millimètres | Utilisations recommandées pour le produit: matelas, canapés, couvertures, vêtements, peluches et lits pour animaux de compagnie | Facteur de forme: Portatif | Couleur: Blanc | Dimensions du produit: 10L x 10l x 10H millimètres</t>
+          <t>Marque: Lubluelu | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Source d'alimentation: Câble électrique | Composants inclus: Brosses rotative | Sans fil ?: Non | Poids de l'article: 1000 Grammes | Utilisations recommandées pour le produit: Matelas, canapés, tapis, couettes, jouets en peluche | Facteur de forme: Portatif | Couleur: Blanc.</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>ALLILUYAA</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés, Matelas Et Jouets en Peluche</t>
+          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirateur à main pour lit, canapé et coussins, contre la poussière et les</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>1 pièce</t>
+          <t>Technologie efficace 3 en 1 contre les acariens et les allergènes : la combinaison de brosse rotative, de fonction de vibration et de soutien thermique aide à éliminer en profondeur les saletés, les acariens et les allergènes profonds dans les tissus, améliorant considérablement l'hygiène des textiles.
+Nettoyage en profondeur puissant de 20 kPa : l'aspirateur anti-acariens puissant élimine de manière fiable la poussière, la saleté et les particules fines des matelas, canapés, tapis, couettes et autres surfaces en tissu, assurant un environnement de vie propre.
+Polyvalent pour différents textiles de la maison : convient pour les matelas, les meubles rembourrés, les tapis, les draps, les couvertures et les jouets en peluche, et idéal pour le nettoyage régulier des chambres, des salons et des zones d'enfants.
+Nettoyage en douceur sans additifs chimiques : le nettoyage est basé sur une technologie mécanique de frappe et de chaleur au lieu de produits chimiques, et est particulièrement adapté aux personnes allergiques, aux familles avec enfants et aux maisons avec animaux domestiques.
+Design compact pour une utilisation quotidienne confortable : câble extra long de 4 mètres pour une portée flexible, appareil à main léger pour une manipulation facile, bac à poussière facile à vider et système de filtration facile d'entretien pour une utilisation pratique au quotidien.</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -13870,13 +13892,11 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>1103214</v>
-      </c>
-      <c r="P37" s="15">
-        <v>-21169</v>
-      </c>
+        <v>1803687</v>
+      </c>
+      <c r="P37" s="15"/>
       <c r="Q37" s="16">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -13885,7 +13905,7 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T37" s="15"/>
@@ -13897,37 +13917,37 @@
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>25.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA37" s="4"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AE37" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF37" s="21">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>6.06</v>
+        <v>8.34</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -13938,14 +13958,14 @@
       <c r="AO37" s="13"/>
       <c r="AP37" s="4"/>
       <c r="AQ37" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR37" s="19">
         <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>ALLILUYAA</t>
+          <t>Lubluelu Official</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
@@ -13960,12 +13980,12 @@
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>bayuquan LiaoNing 115007 CN</t>
+          <t>HuMenZhen GuangDong 523000 CN</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
@@ -13982,43 +14002,43 @@
       <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>430 g</t>
+          <t>1000 Grammes</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>430.00 g</t>
+          <t>1,000.00 g</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>10L x 10l x 10H millimètres</t>
+          <t>42L x 31l x 18H centimètres</t>
         </is>
       </c>
       <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>430 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>430.00 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>25.1 x 20.5 x 11.2 cm</t>
+          <t>33.5 x 26.8 x 25.5 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>25.10 x 20.50 x 11.20 cm</t>
+          <t>33.50 x 26.80 x 25.50 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -14029,52 +14049,52 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Marque: Lubluelu | Caractéristique spéciale: Lumière UV | Recommandation de surface: Tapis | Source d'alimentation: Câble électrique | Composants inclus: Brosses rotative | Sans fil ?: Non | Poids de l'article: 1000 Grammes | Utilisations recommandées pour le produit: Matelas, canapés, tapis, couettes, jouets en peluche | Facteur de forme: Portatif | Couleur: Blanc.</t>
+          <t>Marque: Bcuuozeeing | Caractéristique spéciale: Compacte, Filtre lavable, Réglage en continu de la puissance d'aspiration, Sans sac, Économie d'énergie | Type de filtre: Filtre HEPA | Recommandation de surface: literie, canapé, plafond, sol dur, tapis | Source d'alimentation: Alimentation secteur | Composants inclus: Aspirateur | Sans fil ?: Oui | Puissance en watts: 60 Watts | Temps de charge: 1,5 heures | Longueur du tuyau: 1 Mètres</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>Bcuuozeeing</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirateur à main pour lit, canapé et coussins, contre la poussière et les</t>
+          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapés</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>Technologie efficace 3 en 1 contre les acariens et les allergènes : la combinaison de brosse rotative, de fonction de vibration et de soutien thermique aide à éliminer en profondeur les saletés, les acariens et les allergènes profonds dans les tissus, améliorant considérablement l'hygiène des textiles.
-Nettoyage en profondeur puissant de 20 kPa : l'aspirateur anti-acariens puissant élimine de manière fiable la poussière, la saleté et les particules fines des matelas, canapés, tapis, couettes et autres surfaces en tissu, assurant un environnement de vie propre.
-Polyvalent pour différents textiles de la maison : convient pour les matelas, les meubles rembourrés, les tapis, les draps, les couvertures et les jouets en peluche, et idéal pour le nettoyage régulier des chambres, des salons et des zones d'enfants.
-Nettoyage en douceur sans additifs chimiques : le nettoyage est basé sur une technologie mécanique de frappe et de chaleur au lieu de produits chimiques, et est particulièrement adapté aux personnes allergiques, aux familles avec enfants et aux maisons avec animaux domestiques.
-Design compact pour une utilisation quotidienne confortable : câble extra long de 4 mètres pour une portée flexible, appareil à main léger pour une manipulation facile, bac à poussière facile à vider et système de filtration facile d'entretien pour une utilisation pratique au quotidien.</t>
+          <t>Aspirateur anti-acariens silencieux avec contrôle intelligent de fonction, portable pour toute la maison. L'aspirateur de lit rechargeable sans fil est parfait pour les matelas, les draps et les canapés en tissu.
+Équipé d'un rouleau à percussion et d'une forte puissance d'aspiration pour un nettoyage en profondeur hygiénique. Il élimine efficacement les saletés profondes des textiles et l'aspire immédiatement.
+Élimination fiable des acariens, des bactéries et de la poussière domestique. Idéal pour les personnes allergiques pour créer un environnement de sommeil sain et sans poussière.
+Design de charge sans fil sans câble d'alimentation gênant, taille portable compacte pour une utilisation facile. Le fonctionnement silencieux ne vous dérange ni lors du nettoyage ni dans la maison.
+Nettoyeur de matelas polyvalent pour toutes les surfaces textiles : matelas, lits, oreillers, canapés et rideaux. Un appareil pratique pour le nettoyage quotidien de la maison.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -14088,7 +14108,7 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>1803687</v>
+        <v>230860</v>
       </c>
       <c r="P38" s="15"/>
       <c r="Q38" s="16">
@@ -14101,7 +14121,7 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T38" s="15"/>
@@ -14113,37 +14133,31 @@
         <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>79.99</v>
+        <v>16.9</v>
       </c>
       <c r="AA38" s="4"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
-      <c r="AD38" s="19">
-        <v>23</v>
-      </c>
-      <c r="AE38" s="15">
-        <v>3</v>
-      </c>
-      <c r="AF38" s="21">
-        <v>4.6</v>
-      </c>
+      <c r="AD38" s="19"/>
+      <c r="AE38" s="15"/>
+      <c r="AF38" s="21"/>
       <c r="AG38" s="22">
         <v>0</v>
       </c>
       <c r="AH38" s="20">
-        <v>8.34</v>
+        <v>6.06</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
@@ -14153,15 +14167,13 @@
       <c r="AN38" s="13"/>
       <c r="AO38" s="13"/>
       <c r="AP38" s="4"/>
-      <c r="AQ38" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ38" s="19"/>
       <c r="AR38" s="19">
         <v>1</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Official</t>
+          <t>BozeRICH</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
@@ -14176,12 +14188,12 @@
       </c>
       <c r="AV38" s="14" t="inlineStr">
         <is>
-          <t>HuMenZhen GuangDong 523000 CN</t>
+          <t>LUOHUQU GUANGDONG 518001 CN</t>
         </is>
       </c>
       <c r="AW38" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8</t>
         </is>
       </c>
       <c r="AX38" s="13"/>
@@ -14192,49 +14204,53 @@
       <c r="BC38" s="13"/>
       <c r="BD38" s="13"/>
       <c r="BE38" s="13"/>
-      <c r="BF38" s="13"/>
+      <c r="BF38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
       <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>1000 Grammes</t>
+          <t>550 g</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>1,000.00 g</t>
+          <t>550.00 g</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>42L x 31l x 18H centimètres</t>
+          <t>18L x 10l x 23H centimètres</t>
         </is>
       </c>
       <c r="BM38" s="23"/>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>550 g</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>550.00 g</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>33.5 x 26.8 x 25.5 cm</t>
+          <t>25 x 21 x 11 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>33.50 x 26.80 x 25.50 cm</t>
+          <t>25.00 x 21.00 x 11.00 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -14245,52 +14261,56 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
-        </is>
-      </c>
-      <c r="D39" s="14"/>
+          <t>B0HFSKFZVX</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Couleur: Violet</t>
+        </is>
+      </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Marque: Bcuuozeeing | Caractéristique spéciale: Compacte, Filtre lavable, Réglage en continu de la puissance d'aspiration, Sans sac, Économie d'énergie | Type de filtre: Filtre HEPA | Recommandation de surface: literie, canapé, plafond, sol dur, tapis | Source d'alimentation: Alimentation secteur | Composants inclus: Aspirateur | Sans fil ?: Oui | Puissance en watts: 60 Watts | Temps de charge: 1,5 heures | Longueur du tuyau: 1 Mètres</t>
+          <t>Marque: IERAKOR | Caractéristique spéciale: Lumière UV | Sans fil ?: Non | Utilisations recommandées pour le produit: Matelas, canapés, tapis, couvertures, peluches et vêtements | Facteur de forme: Portatif | Couleur: Violet | Dimensions du produit: 19L x 38l x 28,5H centimètres | Fabricant: IERAKOR | Nombre d'articles: 1</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Bcuuozeeing</t>
+          <t>IERAKOR</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapés</t>
+          <t>IERAKOR Aspirateur Matelas Anti Acariens avec Lumière UV, 16kPa Aspiration</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens silencieux avec contrôle intelligent de fonction, portable pour toute la maison. L'aspirateur de lit rechargeable sans fil est parfait pour les matelas, les draps et les canapés en tissu.
-Équipé d'un rouleau à percussion et d'une forte puissance d'aspiration pour un nettoyage en profondeur hygiénique. Il élimine efficacement les saletés profondes des textiles et l'aspire immédiatement.
-Élimination fiable des acariens, des bactéries et de la poussière domestique. Idéal pour les personnes allergiques pour créer un environnement de sommeil sain et sans poussière.
-Design de charge sans fil sans câble d'alimentation gênant, taille portable compacte pour une utilisation facile. Le fonctionnement silencieux ne vous dérange ni lors du nettoyage ni dans la maison.
-Nettoyeur de matelas polyvalent pour toutes les surfaces textiles : matelas, lits, oreillers, canapés et rideaux. Un appareil pratique pour le nettoyage quotidien de la maison.</t>
+          <t>💪【Aspiration 16kPa】Équipé d'un moteur haute performance de 600 W et d'un système Rotavator puissant générant 36 000 pulsations par minute, cet aspirateur anti-acariens offre une aspiration exceptionnelle de 16 000 Pa. Il extrait en profondeur la poussière, les squames et les poils d'animaux des fibres les plus denses.
+🔄【Système de filtration multi-étapes】Contrairement aux modèles traditionnels, cet aspirateur est doté d'un système de circulation d'air unique à double compartiment à poussière et d'une grande capacité de 0,5 L. Une technologie avancée de séparation cyclonique sépare efficacement l'air de la poussière, évitant ainsi le colmatage du filtre et garantissant une puissance d'aspiration élevée et constante tout au long du nettoyage.
+🛡️【Nettoyage par UV profonds (253,7 nm)】Cet aspirateur pour matelas est équipé d'une lampe UV de 253,7 nm qui aide à éliminer les acariens et les particules nocives, créant ainsi un environnement plus propre et plus sain. Sa fonction de diffusion d'air chaud à 60 °C (140 °F) sèche le matelas et élimine l'humidité dont les acariens ont besoin pour proliférer, préservant ainsi la qualité du sommeil des adultes et des personnes âgées.
+⚙️【Brosse Rotative 80° &amp; Câble 4M】La tête de brosse présente une conception flexible pivotant jusqu'à 80 degrés ; elle épouse sans effort les formes des lits, des canapés et des coussins pour un nettoyage complet, sans zones oubliées. Associée à un câble d'alimentation extra-long de 4 mètres et à un débit d'air maximal de 1,2 m³/min, elle offre une plus grande liberté de mouvement et une portée étendue pour le nettoyage de votre chambre ou de votre salon.
+🏠【Adapté à de multiples usages dans toute la maison】Cet aspirateur anti-acariens est idéal pour nettoyer matelas, canapés, tapis, couvertures, peluches et vêtements. Sa brosse rotative douce préserve les tissus délicats. Qu'il s'agisse de l'entretien quotidien, du nettoyage en profondeur des canapés ou d'une utilisation à l'hôtel, en appartement, au camping ou en voyage, c'est un compagnon de nettoyage idéal.</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFSKFZVX?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HKH3YCFW</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -14304,7 +14324,7 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>230860</v>
+        <v>593244</v>
       </c>
       <c r="P39" s="15"/>
       <c r="Q39" s="16">
@@ -14317,7 +14337,7 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T39" s="15"/>
@@ -14326,34 +14346,38 @@
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="20">
-        <v>16.9</v>
+        <v>89.99</v>
       </c>
       <c r="AA39" s="4"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
-      <c r="AD39" s="19"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="21"/>
+      <c r="AD39" s="19">
+        <v>8</v>
+      </c>
+      <c r="AE39" s="15">
+        <v>2</v>
+      </c>
+      <c r="AF39" s="21">
+        <v>5</v>
+      </c>
       <c r="AG39" s="22">
         <v>0</v>
       </c>
-      <c r="AH39" s="20">
-        <v>6.06</v>
-      </c>
+      <c r="AH39" s="20"/>
       <c r="AI39" s="16">
-        <v>0.49</v>
+        <v>0.85</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -14363,13 +14387,15 @@
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39" s="4"/>
-      <c r="AQ39" s="19"/>
+      <c r="AQ39" s="19">
+        <v>9</v>
+      </c>
       <c r="AR39" s="19">
         <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>BozeRICH</t>
+          <t>aijuzhang_01</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
@@ -14379,17 +14405,17 @@
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>LUOHUQU GUANGDONG 518001 CN</t>
+          <t>KWAI CHUNG HONG KONG 999077 HK</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
@@ -14397,256 +14423,34 @@
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
-      <c r="BC39" s="13"/>
-      <c r="BD39" s="13"/>
+      <c r="BC39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="13"/>
-      <c r="BF39" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
       <c r="BI39" s="23"/>
-      <c r="BJ39" s="23" t="inlineStr">
-        <is>
-          <t>550 g</t>
-        </is>
-      </c>
-      <c r="BK39" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
+      <c r="BJ39" s="23"/>
+      <c r="BK39" s="23"/>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>18L x 10l x 23H centimètres</t>
+          <t>19L x 38l x 28,5H centimètres</t>
         </is>
       </c>
       <c r="BM39" s="23"/>
-      <c r="BN39" s="23" t="inlineStr">
-        <is>
-          <t>550 g</t>
-        </is>
-      </c>
-      <c r="BO39" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BP39" s="23" t="inlineStr">
-        <is>
-          <t>25 x 21 x 11 cm</t>
-        </is>
-      </c>
-      <c r="BQ39" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 21.00 x 11.00 cm</t>
-        </is>
-      </c>
-      <c r="BR39" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13">
-        <v>39</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>B0HFSKFZVX</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Couleur: Violet</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Marque: IERAKOR | Caractéristique spéciale: Lumière UV | Sans fil ?: Non | Utilisations recommandées pour le produit: Matelas, canapés, tapis, couvertures, peluches et vêtements | Facteur de forme: Portatif | Couleur: Violet | Dimensions du produit: 19L x 38l x 28,5H centimètres | Fabricant: IERAKOR | Nombre d'articles: 1</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>IERAKOR</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>IERAKOR Aspirateur Matelas Anti Acariens avec Lumière UV, 16kPa Aspiration</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>💪【Aspiration 16kPa】Équipé d'un moteur haute performance de 600 W et d'un système Rotavator puissant générant 36 000 pulsations par minute, cet aspirateur anti-acariens offre une aspiration exceptionnelle de 16 000 Pa. Il extrait en profondeur la poussière, les squames et les poils d'animaux des fibres les plus denses.
-🔄【Système de filtration multi-étapes】Contrairement aux modèles traditionnels, cet aspirateur est doté d'un système de circulation d'air unique à double compartiment à poussière et d'une grande capacité de 0,5 L. Une technologie avancée de séparation cyclonique sépare efficacement l'air de la poussière, évitant ainsi le colmatage du filtre et garantissant une puissance d'aspiration élevée et constante tout au long du nettoyage.
-🛡️【Nettoyage par UV profonds (253,7 nm)】Cet aspirateur pour matelas est équipé d'une lampe UV de 253,7 nm qui aide à éliminer les acariens et les particules nocives, créant ainsi un environnement plus propre et plus sain. Sa fonction de diffusion d'air chaud à 60 °C (140 °F) sèche le matelas et élimine l'humidité dont les acariens ont besoin pour proliférer, préservant ainsi la qualité du sommeil des adultes et des personnes âgées.
-⚙️【Brosse Rotative 80° &amp; Câble 4M】La tête de brosse présente une conception flexible pivotant jusqu'à 80 degrés ; elle épouse sans effort les formes des lits, des canapés et des coussins pour un nettoyage complet, sans zones oubliées. Associée à un câble d'alimentation extra-long de 4 mètres et à un débit d'air maximal de 1,2 m³/min, elle offre une plus grande liberté de mouvement et une portée étendue pour le nettoyage de votre chambre ou de votre salon.
-🏠【Adapté à de multiples usages dans toute la maison】Cet aspirateur anti-acariens est idéal pour nettoyer matelas, canapés, tapis, couvertures, peluches et vêtements. Sa brosse rotative douce préserve les tissus délicats. Qu'il s'agisse de l'entretien quotidien, du nettoyage en profondeur des canapés ou d'une utilisation à l'hôtel, en appartement, au camping ou en voyage, c'est un compagnon de nettoyage idéal.</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HFSKFZVX?psc=1</t>
-        </is>
-      </c>
-      <c r="K40" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L40" s="14" t="inlineStr">
-        <is>
-          <t>B0HKH3YCFW</t>
-        </is>
-      </c>
-      <c r="M40" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O40" s="15">
-        <v>593244</v>
-      </c>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="16">
-        <v>0</v>
-      </c>
-      <c r="R40" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S40" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T40" s="15"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>89.99</v>
-      </c>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>8</v>
-      </c>
-      <c r="AE40" s="15">
-        <v>2</v>
-      </c>
-      <c r="AF40" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG40" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="20"/>
-      <c r="AI40" s="16">
-        <v>0.85</v>
-      </c>
-      <c r="AJ40"/>
-      <c r="AK40" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AL40" s="19">
-        <v>32</v>
-      </c>
-      <c r="AM40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN40" s="13"/>
-      <c r="AO40" s="13"/>
-      <c r="AP40" s="4"/>
-      <c r="AQ40" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR40" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS40" s="14" t="inlineStr">
-        <is>
-          <t>aijuzhang_01</t>
-        </is>
-      </c>
-      <c r="AT40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV40" s="14" t="inlineStr">
-        <is>
-          <t>KWAI CHUNG HONG KONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB</t>
-        </is>
-      </c>
-      <c r="AX40" s="13"/>
-      <c r="AY40" s="13"/>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="13"/>
-      <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE40" s="13"/>
-      <c r="BF40" s="13"/>
-      <c r="BG40" s="13"/>
-      <c r="BH40" s="14"/>
-      <c r="BI40" s="23"/>
-      <c r="BJ40" s="23"/>
-      <c r="BK40" s="23"/>
-      <c r="BL40" s="23" t="inlineStr">
-        <is>
-          <t>19L x 38l x 28,5H centimètres</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
-      <c r="BN40" s="23"/>
-      <c r="BO40" s="23"/>
-      <c r="BP40" s="23"/>
-      <c r="BQ40" s="23"/>
-      <c r="BR40" s="13"/>
+      <c r="BN39" s="23"/>
+      <c r="BO39" s="23"/>
+      <c r="BP39" s="23"/>
+      <c r="BQ39" s="23"/>
+      <c r="BR39" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14834,138 +14638,130 @@
     <hyperlink ref="M24" r:id="rId180" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N24" r:id="rId181"/>
     <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF"/>
-    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Hocomay"/>
-    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1"/>
-    <hyperlink ref="K25" r:id="rId186" tooltip="https://images-na.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
+    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln"/>
+    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K25" r:id="rId186" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
     <hyperlink ref="M25" r:id="rId188" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N25" r:id="rId189"/>
-    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JWI8CSWZ8XWG"/>
-    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln"/>
-    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
+    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K26" r:id="rId194" tooltip="https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
     <hyperlink ref="M26" r:id="rId196" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N26" r:id="rId197"/>
-    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
-    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K27" r:id="rId202" tooltip="https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="M27" r:id="rId204" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N27" r:id="rId205"/>
-    <hyperlink ref="C28" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="G28" r:id="rId207" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K28" r:id="rId209" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="M28" r:id="rId211" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N28" r:id="rId212"/>
-    <hyperlink ref="C29" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="G29" r:id="rId214" tooltip="https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz"/>
-    <hyperlink ref="J29" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId217" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="C27" r:id="rId198" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="G27" r:id="rId199" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId200" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K27" r:id="rId201" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId202" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="M27" r:id="rId203" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N27" r:id="rId204"/>
+    <hyperlink ref="C28" r:id="rId205" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="G28" r:id="rId206" tooltip="https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz"/>
+    <hyperlink ref="J28" r:id="rId207" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
+    <hyperlink ref="K28" r:id="rId208" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId209" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="M28" r:id="rId210" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N28" r:id="rId211"/>
+    <hyperlink ref="AW28" r:id="rId212" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
+    <hyperlink ref="C29" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="G29" r:id="rId214" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J29" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K29" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId217" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
     <hyperlink ref="M29" r:id="rId218" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N29" r:id="rId219"/>
-    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
-    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K30" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K30" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0HHRGDS1P"/>
     <hyperlink ref="M30" r:id="rId226" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N30" r:id="rId227"/>
-    <hyperlink ref="AW30" r:id="rId228" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C31" r:id="rId229" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
-    <hyperlink ref="G31" r:id="rId230" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K31" r:id="rId232" tooltip="https://images-na.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0HHRGDS1P"/>
-    <hyperlink ref="M31" r:id="rId234" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N31" r:id="rId235"/>
-    <hyperlink ref="C32" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="G32" r:id="rId237" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J32" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K32" r:id="rId239" tooltip="https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="M32" r:id="rId241" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N32" r:id="rId242"/>
-    <hyperlink ref="C33" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="G33" r:id="rId244" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric"/>
-    <hyperlink ref="J33" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
-    <hyperlink ref="K33" r:id="rId246" tooltip="https://images-na.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="C31" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="G31" r:id="rId229" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J31" r:id="rId230" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K31" r:id="rId231" tooltip="https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId232" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="M31" r:id="rId233" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N31" r:id="rId234"/>
+    <hyperlink ref="C32" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="G32" r:id="rId236" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric"/>
+    <hyperlink ref="J32" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
+    <hyperlink ref="K32" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="M32" r:id="rId240" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N32" r:id="rId241"/>
+    <hyperlink ref="AW32" r:id="rId242" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42"/>
+    <hyperlink ref="C33" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="G33" r:id="rId244" tooltip="https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee"/>
+    <hyperlink ref="J33" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
+    <hyperlink ref="K33" r:id="rId246" tooltip="https://images-na.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0HJRR2QDH"/>
     <hyperlink ref="M33" r:id="rId248" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N33" r:id="rId249"/>
-    <hyperlink ref="AW33" r:id="rId250" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42"/>
-    <hyperlink ref="C34" r:id="rId251" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="G34" r:id="rId252" tooltip="https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee"/>
-    <hyperlink ref="J34" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
-    <hyperlink ref="K34" r:id="rId254" tooltip="https://images-na.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0HJRR2QDH"/>
+    <hyperlink ref="AW33" r:id="rId250" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
+    <hyperlink ref="C34" r:id="rId251" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="G34" r:id="rId252" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
+    <hyperlink ref="J34" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K34" r:id="rId254" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0GXBVPPWQ"/>
     <hyperlink ref="M34" r:id="rId256" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N34" r:id="rId257"/>
-    <hyperlink ref="AW34" r:id="rId258" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
-    <hyperlink ref="C35" r:id="rId259" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="G35" r:id="rId260" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
-    <hyperlink ref="J35" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K35" r:id="rId262" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0GXBVPPWQ"/>
+    <hyperlink ref="AW34" r:id="rId258" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
+    <hyperlink ref="C35" r:id="rId259" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="G35" r:id="rId260" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
+    <hyperlink ref="J35" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
+    <hyperlink ref="K35" r:id="rId262" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
     <hyperlink ref="M35" r:id="rId264" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N35" r:id="rId265"/>
-    <hyperlink ref="AW35" r:id="rId266" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
-    <hyperlink ref="C36" r:id="rId267" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="G36" r:id="rId268" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
-    <hyperlink ref="J36" r:id="rId269" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
-    <hyperlink ref="K36" r:id="rId270" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId271" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="AW35" r:id="rId266" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
+    <hyperlink ref="C36" r:id="rId267" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="G36" r:id="rId268" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId269" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K36" r:id="rId270" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId271" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
     <hyperlink ref="M36" r:id="rId272" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N36" r:id="rId273"/>
-    <hyperlink ref="AW36" r:id="rId274" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
-    <hyperlink ref="C37" r:id="rId275" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="G37" r:id="rId276" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId277" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K37" r:id="rId278" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId279" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="AW36" r:id="rId274" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
+    <hyperlink ref="C37" r:id="rId275" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="G37" r:id="rId276" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId277" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
+    <hyperlink ref="K37" r:id="rId278" tooltip="https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId279" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
     <hyperlink ref="M37" r:id="rId280" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N37" r:id="rId281"/>
-    <hyperlink ref="AW37" r:id="rId282" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
-    <hyperlink ref="C38" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="G38" r:id="rId284" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
-    <hyperlink ref="K38" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId287" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="AW37" r:id="rId282" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
+    <hyperlink ref="C38" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="G38" r:id="rId284" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
+    <hyperlink ref="J38" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K38" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId287" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
     <hyperlink ref="M38" r:id="rId288" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N38" r:id="rId289"/>
-    <hyperlink ref="AW38" r:id="rId290" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
-    <hyperlink ref="C39" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="G39" r:id="rId292" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
-    <hyperlink ref="J39" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K39" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="AW38" r:id="rId290" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8"/>
+    <hyperlink ref="C39" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
+    <hyperlink ref="G39" r:id="rId292" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR"/>
+    <hyperlink ref="J39" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX?psc=1"/>
+    <hyperlink ref="K39" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0HKH3YCFW"/>
     <hyperlink ref="M39" r:id="rId296" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N39" r:id="rId297"/>
-    <hyperlink ref="AW39" r:id="rId298" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8"/>
-    <hyperlink ref="C40" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
-    <hyperlink ref="G40" r:id="rId300" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR"/>
-    <hyperlink ref="J40" r:id="rId301" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX?psc=1"/>
-    <hyperlink ref="K40" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0HKH3YCFW"/>
-    <hyperlink ref="M40" r:id="rId304" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N40" r:id="rId305"/>
-    <hyperlink ref="AW40" r:id="rId306" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB"/>
+    <hyperlink ref="AW39" r:id="rId298" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB"/>
   </hyperlinks>
-  <drawing r:id="rId307"/>
+  <drawing r:id="rId299"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -15363,7 +15159,7 @@
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Hocomay</t>
+          <t>IERAKOR</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -15382,7 +15178,7 @@
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>IERAKOR</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -15401,7 +15197,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Minthouz</t>
+          <t>Nastopee</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -15420,7 +15216,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Nastopee</t>
+          <t>SIKITUT</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -15439,7 +15235,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>SIKITUT</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -15458,7 +15254,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Timisea</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -15477,7 +15273,7 @@
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Timisea</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="B25" s="15">
@@ -15496,7 +15292,7 @@
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>Vihoom</t>
         </is>
       </c>
       <c r="B26" s="15">
@@ -15515,7 +15311,7 @@
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Vihoom</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="B27" s="15">
@@ -15528,25 +15324,6 @@
       <c r="E27" s="15"/>
       <c r="F27" s="20"/>
       <c r="G27" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>XINYUDAILY</t>
-        </is>
-      </c>
-      <c r="B28" s="15">
-        <v>0</v>
-      </c>
-      <c r="C28" s="15">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -15558,7 +15335,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -15998,7 +15775,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Luckily Baby</t>
+          <t>Minthouz EUDirect</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -16017,7 +15794,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Minthouz EUDirect</t>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -16036,7 +15813,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
+          <t>PETERTOS Kft.</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -16055,7 +15832,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PETERTOS Kft.</t>
+          <t>SILVER LION Limited</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -16074,7 +15851,7 @@
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>SILVER LION Limited</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="B25" s="15">
@@ -16093,7 +15870,7 @@
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B26" s="15">
@@ -16112,7 +15889,7 @@
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
         </is>
       </c>
       <c r="B27" s="15">
@@ -16131,7 +15908,7 @@
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>XINYU-EU</t>
         </is>
       </c>
       <c r="B28" s="15">
@@ -16150,7 +15927,7 @@
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Yumujo</t>
         </is>
       </c>
       <c r="B29" s="15">
@@ -16169,7 +15946,7 @@
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Yumujo</t>
+          <t>aijuzhang_01</t>
         </is>
       </c>
       <c r="B30" s="15">
@@ -16188,7 +15965,7 @@
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>aijuzhang_01</t>
+          <t>eusmarthousehold</t>
         </is>
       </c>
       <c r="B31" s="15">
@@ -16201,25 +15978,6 @@
       <c r="E31" s="15"/>
       <c r="F31" s="20"/>
       <c r="G31" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>eusmarthousehold</t>
-        </is>
-      </c>
-      <c r="B32" s="15">
-        <v>0</v>
-      </c>
-      <c r="C32" s="15">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="22">
         <v>0.0</v>
       </c>
     </row>
